--- a/uvoz/GradnjaOS-uvoz-sablon.xlsx
+++ b/uvoz/GradnjaOS-uvoz-sablon.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Gradilišta'!$A$1:$Z$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Tim'!$A$1:$C$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Predmer'!$A$1:$H$500</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Zadaci'!$A$1:$G$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Zadaci'!$A$1:$H$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Dnevnik'!$A$1:$E$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Troškovi'!$A$1:$H$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Situacije'!$A$1:$H$500</definedName>
@@ -638,20 +638,25 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>id iz lista Zaposleni</t>
+        <t>Duži opis zadatka (opciono)</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>high | mid | low</t>
+        <t>id iz lista Zaposleni</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
+        <t>high | mid | low</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
         <t>todo | inprogress | hold | done</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>OBAVEZNO. datum GGGG-MM-DD (ili Excel datum)</t>
       </text>
@@ -55313,16 +55318,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G500"/>
+  <dimension ref="A1:H500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -55343,20 +55349,25 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>zaduzen_id</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>prio</t>
+          <t>zaduzen_id</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
+          <t>prio</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
           <t>kolona</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>rok</t>
         </is>
@@ -55376,20 +55387,25 @@
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>Z-01</t>
+          <t>Ø12 na 15 cm, gornja zona</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
           <t>inprogress</t>
         </is>
       </c>
-      <c r="G2" s="13" t="inlineStr">
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
@@ -55402,7 +55418,8 @@
       <c r="D3" s="11" t="n"/>
       <c r="E3" s="11" t="n"/>
       <c r="F3" s="11" t="n"/>
-      <c r="G3" s="14" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="n"/>
@@ -55411,7 +55428,8 @@
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="11" t="n"/>
-      <c r="G4" s="14" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n"/>
@@ -55420,7 +55438,8 @@
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="11" t="n"/>
-      <c r="G5" s="14" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n"/>
@@ -55429,7 +55448,8 @@
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="11" t="n"/>
       <c r="F6" s="11" t="n"/>
-      <c r="G6" s="14" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n"/>
@@ -55438,7 +55458,8 @@
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
-      <c r="G7" s="14" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n"/>
@@ -55447,7 +55468,8 @@
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="11" t="n"/>
       <c r="F8" s="11" t="n"/>
-      <c r="G8" s="14" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n"/>
@@ -55456,7 +55478,8 @@
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
-      <c r="G9" s="14" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="n"/>
@@ -55465,7 +55488,8 @@
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="11" t="n"/>
-      <c r="G10" s="14" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n"/>
@@ -55474,7 +55498,8 @@
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="11" t="n"/>
-      <c r="G11" s="14" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n"/>
@@ -55483,7 +55508,8 @@
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="11" t="n"/>
-      <c r="G12" s="14" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n"/>
@@ -55492,7 +55518,8 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="11" t="n"/>
-      <c r="G13" s="14" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="n"/>
@@ -55501,7 +55528,8 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="11" t="n"/>
-      <c r="G14" s="14" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n"/>
@@ -55510,7 +55538,8 @@
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="14" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="n"/>
@@ -55519,7 +55548,8 @@
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="11" t="n"/>
-      <c r="G16" s="14" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n"/>
@@ -55528,7 +55558,8 @@
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="11" t="n"/>
-      <c r="G17" s="14" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n"/>
@@ -55537,7 +55568,8 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
-      <c r="G18" s="14" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n"/>
@@ -55546,7 +55578,8 @@
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="11" t="n"/>
-      <c r="G19" s="14" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="n"/>
@@ -55555,7 +55588,8 @@
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
-      <c r="G20" s="14" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n"/>
@@ -55564,7 +55598,8 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="11" t="n"/>
-      <c r="G21" s="14" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n"/>
@@ -55573,7 +55608,8 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="11" t="n"/>
-      <c r="G22" s="14" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n"/>
@@ -55582,7 +55618,8 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="11" t="n"/>
-      <c r="G23" s="14" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n"/>
@@ -55591,7 +55628,8 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="11" t="n"/>
-      <c r="G24" s="14" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n"/>
@@ -55600,7 +55638,8 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="11" t="n"/>
-      <c r="G25" s="14" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n"/>
@@ -55609,7 +55648,8 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="11" t="n"/>
-      <c r="G26" s="14" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n"/>
@@ -55618,7 +55658,8 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="11" t="n"/>
-      <c r="G27" s="14" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="n"/>
@@ -55627,7 +55668,8 @@
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="11" t="n"/>
-      <c r="G28" s="14" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n"/>
@@ -55636,7 +55678,8 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="11" t="n"/>
-      <c r="G29" s="14" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="n"/>
@@ -55645,7 +55688,8 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="14" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n"/>
@@ -55654,7 +55698,8 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="14" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="n"/>
@@ -55663,7 +55708,8 @@
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="14" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n"/>
@@ -55672,7 +55718,8 @@
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="14" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="n"/>
@@ -55681,7 +55728,8 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="11" t="n"/>
-      <c r="G34" s="14" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n"/>
@@ -55690,7 +55738,8 @@
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="11" t="n"/>
-      <c r="G35" s="14" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="n"/>
@@ -55699,7 +55748,8 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="11" t="n"/>
-      <c r="G36" s="14" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n"/>
@@ -55708,7 +55758,8 @@
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="11" t="n"/>
-      <c r="G37" s="14" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="n"/>
@@ -55717,7 +55768,8 @@
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="11" t="n"/>
-      <c r="G38" s="14" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n"/>
@@ -55726,7 +55778,8 @@
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="11" t="n"/>
-      <c r="G39" s="14" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="n"/>
@@ -55735,7 +55788,8 @@
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="11" t="n"/>
-      <c r="G40" s="14" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n"/>
@@ -55744,7 +55798,8 @@
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="11" t="n"/>
-      <c r="G41" s="14" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="n"/>
@@ -55753,7 +55808,8 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
-      <c r="G42" s="14" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n"/>
@@ -55762,7 +55818,8 @@
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="n"/>
-      <c r="G43" s="14" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="n"/>
@@ -55771,7 +55828,8 @@
       <c r="D44" s="11" t="n"/>
       <c r="E44" s="11" t="n"/>
       <c r="F44" s="11" t="n"/>
-      <c r="G44" s="14" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n"/>
@@ -55780,7 +55838,8 @@
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
-      <c r="G45" s="14" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n"/>
@@ -55789,7 +55848,8 @@
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
-      <c r="G46" s="14" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n"/>
@@ -55798,7 +55858,8 @@
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="11" t="n"/>
-      <c r="G47" s="14" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="n"/>
@@ -55807,7 +55868,8 @@
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="11" t="n"/>
       <c r="F48" s="11" t="n"/>
-      <c r="G48" s="14" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n"/>
@@ -55816,7 +55878,8 @@
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="11" t="n"/>
-      <c r="G49" s="14" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="n"/>
@@ -55825,7 +55888,8 @@
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
-      <c r="G50" s="14" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n"/>
@@ -55834,7 +55898,8 @@
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="11" t="n"/>
       <c r="F51" s="11" t="n"/>
-      <c r="G51" s="14" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="n"/>
@@ -55843,7 +55908,8 @@
       <c r="D52" s="11" t="n"/>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
-      <c r="G52" s="14" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n"/>
@@ -55852,7 +55918,8 @@
       <c r="D53" s="11" t="n"/>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
-      <c r="G53" s="14" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="n"/>
@@ -55861,7 +55928,8 @@
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
-      <c r="G54" s="14" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n"/>
@@ -55870,7 +55938,8 @@
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="11" t="n"/>
       <c r="F55" s="11" t="n"/>
-      <c r="G55" s="14" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="n"/>
@@ -55879,7 +55948,8 @@
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="11" t="n"/>
       <c r="F56" s="11" t="n"/>
-      <c r="G56" s="14" t="n"/>
+      <c r="G56" s="11" t="n"/>
+      <c r="H56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n"/>
@@ -55888,7 +55958,8 @@
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="11" t="n"/>
-      <c r="G57" s="14" t="n"/>
+      <c r="G57" s="11" t="n"/>
+      <c r="H57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="n"/>
@@ -55897,7 +55968,8 @@
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="11" t="n"/>
       <c r="F58" s="11" t="n"/>
-      <c r="G58" s="14" t="n"/>
+      <c r="G58" s="11" t="n"/>
+      <c r="H58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="n"/>
@@ -55906,7 +55978,8 @@
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="11" t="n"/>
       <c r="F59" s="11" t="n"/>
-      <c r="G59" s="14" t="n"/>
+      <c r="G59" s="11" t="n"/>
+      <c r="H59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="n"/>
@@ -55915,7 +55988,8 @@
       <c r="D60" s="11" t="n"/>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
-      <c r="G60" s="14" t="n"/>
+      <c r="G60" s="11" t="n"/>
+      <c r="H60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="n"/>
@@ -55924,7 +55998,8 @@
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="11" t="n"/>
       <c r="F61" s="11" t="n"/>
-      <c r="G61" s="14" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="n"/>
@@ -55933,7 +56008,8 @@
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
-      <c r="G62" s="14" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="n"/>
@@ -55942,7 +56018,8 @@
       <c r="D63" s="11" t="n"/>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
-      <c r="G63" s="14" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="n"/>
@@ -55951,7 +56028,8 @@
       <c r="D64" s="11" t="n"/>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
-      <c r="G64" s="14" t="n"/>
+      <c r="G64" s="11" t="n"/>
+      <c r="H64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="n"/>
@@ -55960,7 +56038,8 @@
       <c r="D65" s="11" t="n"/>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
-      <c r="G65" s="14" t="n"/>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="n"/>
@@ -55969,7 +56048,8 @@
       <c r="D66" s="11" t="n"/>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
-      <c r="G66" s="14" t="n"/>
+      <c r="G66" s="11" t="n"/>
+      <c r="H66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="n"/>
@@ -55978,7 +56058,8 @@
       <c r="D67" s="11" t="n"/>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
-      <c r="G67" s="14" t="n"/>
+      <c r="G67" s="11" t="n"/>
+      <c r="H67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="11" t="n"/>
@@ -55987,7 +56068,8 @@
       <c r="D68" s="11" t="n"/>
       <c r="E68" s="11" t="n"/>
       <c r="F68" s="11" t="n"/>
-      <c r="G68" s="14" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="11" t="n"/>
@@ -55996,7 +56078,8 @@
       <c r="D69" s="11" t="n"/>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
-      <c r="G69" s="14" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n"/>
@@ -56005,7 +56088,8 @@
       <c r="D70" s="11" t="n"/>
       <c r="E70" s="11" t="n"/>
       <c r="F70" s="11" t="n"/>
-      <c r="G70" s="14" t="n"/>
+      <c r="G70" s="11" t="n"/>
+      <c r="H70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n"/>
@@ -56014,7 +56098,8 @@
       <c r="D71" s="11" t="n"/>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
-      <c r="G71" s="14" t="n"/>
+      <c r="G71" s="11" t="n"/>
+      <c r="H71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n"/>
@@ -56023,7 +56108,8 @@
       <c r="D72" s="11" t="n"/>
       <c r="E72" s="11" t="n"/>
       <c r="F72" s="11" t="n"/>
-      <c r="G72" s="14" t="n"/>
+      <c r="G72" s="11" t="n"/>
+      <c r="H72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="11" t="n"/>
@@ -56032,7 +56118,8 @@
       <c r="D73" s="11" t="n"/>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
-      <c r="G73" s="14" t="n"/>
+      <c r="G73" s="11" t="n"/>
+      <c r="H73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="11" t="n"/>
@@ -56041,7 +56128,8 @@
       <c r="D74" s="11" t="n"/>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
-      <c r="G74" s="14" t="n"/>
+      <c r="G74" s="11" t="n"/>
+      <c r="H74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="11" t="n"/>
@@ -56050,7 +56138,8 @@
       <c r="D75" s="11" t="n"/>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
-      <c r="G75" s="14" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="11" t="n"/>
@@ -56059,7 +56148,8 @@
       <c r="D76" s="11" t="n"/>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
-      <c r="G76" s="14" t="n"/>
+      <c r="G76" s="11" t="n"/>
+      <c r="H76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="11" t="n"/>
@@ -56068,7 +56158,8 @@
       <c r="D77" s="11" t="n"/>
       <c r="E77" s="11" t="n"/>
       <c r="F77" s="11" t="n"/>
-      <c r="G77" s="14" t="n"/>
+      <c r="G77" s="11" t="n"/>
+      <c r="H77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="11" t="n"/>
@@ -56077,7 +56168,8 @@
       <c r="D78" s="11" t="n"/>
       <c r="E78" s="11" t="n"/>
       <c r="F78" s="11" t="n"/>
-      <c r="G78" s="14" t="n"/>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="11" t="n"/>
@@ -56086,7 +56178,8 @@
       <c r="D79" s="11" t="n"/>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
-      <c r="G79" s="14" t="n"/>
+      <c r="G79" s="11" t="n"/>
+      <c r="H79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="11" t="n"/>
@@ -56095,7 +56188,8 @@
       <c r="D80" s="11" t="n"/>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
-      <c r="G80" s="14" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="11" t="n"/>
@@ -56104,7 +56198,8 @@
       <c r="D81" s="11" t="n"/>
       <c r="E81" s="11" t="n"/>
       <c r="F81" s="11" t="n"/>
-      <c r="G81" s="14" t="n"/>
+      <c r="G81" s="11" t="n"/>
+      <c r="H81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n"/>
@@ -56113,7 +56208,8 @@
       <c r="D82" s="11" t="n"/>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
-      <c r="G82" s="14" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n"/>
@@ -56122,7 +56218,8 @@
       <c r="D83" s="11" t="n"/>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
-      <c r="G83" s="14" t="n"/>
+      <c r="G83" s="11" t="n"/>
+      <c r="H83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n"/>
@@ -56131,7 +56228,8 @@
       <c r="D84" s="11" t="n"/>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
-      <c r="G84" s="14" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="11" t="n"/>
@@ -56140,7 +56238,8 @@
       <c r="D85" s="11" t="n"/>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
-      <c r="G85" s="14" t="n"/>
+      <c r="G85" s="11" t="n"/>
+      <c r="H85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="11" t="n"/>
@@ -56149,7 +56248,8 @@
       <c r="D86" s="11" t="n"/>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
-      <c r="G86" s="14" t="n"/>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="n"/>
@@ -56158,7 +56258,8 @@
       <c r="D87" s="11" t="n"/>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
-      <c r="G87" s="14" t="n"/>
+      <c r="G87" s="11" t="n"/>
+      <c r="H87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="11" t="n"/>
@@ -56167,7 +56268,8 @@
       <c r="D88" s="11" t="n"/>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
-      <c r="G88" s="14" t="n"/>
+      <c r="G88" s="11" t="n"/>
+      <c r="H88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="11" t="n"/>
@@ -56176,7 +56278,8 @@
       <c r="D89" s="11" t="n"/>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
-      <c r="G89" s="14" t="n"/>
+      <c r="G89" s="11" t="n"/>
+      <c r="H89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="11" t="n"/>
@@ -56185,7 +56288,8 @@
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
-      <c r="G90" s="14" t="n"/>
+      <c r="G90" s="11" t="n"/>
+      <c r="H90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="11" t="n"/>
@@ -56194,7 +56298,8 @@
       <c r="D91" s="11" t="n"/>
       <c r="E91" s="11" t="n"/>
       <c r="F91" s="11" t="n"/>
-      <c r="G91" s="14" t="n"/>
+      <c r="G91" s="11" t="n"/>
+      <c r="H91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="11" t="n"/>
@@ -56203,7 +56308,8 @@
       <c r="D92" s="11" t="n"/>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
-      <c r="G92" s="14" t="n"/>
+      <c r="G92" s="11" t="n"/>
+      <c r="H92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="n"/>
@@ -56212,7 +56318,8 @@
       <c r="D93" s="11" t="n"/>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
-      <c r="G93" s="14" t="n"/>
+      <c r="G93" s="11" t="n"/>
+      <c r="H93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="11" t="n"/>
@@ -56221,7 +56328,8 @@
       <c r="D94" s="11" t="n"/>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
-      <c r="G94" s="14" t="n"/>
+      <c r="G94" s="11" t="n"/>
+      <c r="H94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="11" t="n"/>
@@ -56230,7 +56338,8 @@
       <c r="D95" s="11" t="n"/>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
-      <c r="G95" s="14" t="n"/>
+      <c r="G95" s="11" t="n"/>
+      <c r="H95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="11" t="n"/>
@@ -56239,7 +56348,8 @@
       <c r="D96" s="11" t="n"/>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
-      <c r="G96" s="14" t="n"/>
+      <c r="G96" s="11" t="n"/>
+      <c r="H96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="11" t="n"/>
@@ -56248,7 +56358,8 @@
       <c r="D97" s="11" t="n"/>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
-      <c r="G97" s="14" t="n"/>
+      <c r="G97" s="11" t="n"/>
+      <c r="H97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="11" t="n"/>
@@ -56257,7 +56368,8 @@
       <c r="D98" s="11" t="n"/>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
-      <c r="G98" s="14" t="n"/>
+      <c r="G98" s="11" t="n"/>
+      <c r="H98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="11" t="n"/>
@@ -56266,7 +56378,8 @@
       <c r="D99" s="11" t="n"/>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
-      <c r="G99" s="14" t="n"/>
+      <c r="G99" s="11" t="n"/>
+      <c r="H99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n"/>
@@ -56275,7 +56388,8 @@
       <c r="D100" s="11" t="n"/>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
-      <c r="G100" s="14" t="n"/>
+      <c r="G100" s="11" t="n"/>
+      <c r="H100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="11" t="n"/>
@@ -56284,7 +56398,8 @@
       <c r="D101" s="11" t="n"/>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
-      <c r="G101" s="14" t="n"/>
+      <c r="G101" s="11" t="n"/>
+      <c r="H101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="n"/>
@@ -56293,7 +56408,8 @@
       <c r="D102" s="11" t="n"/>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
-      <c r="G102" s="14" t="n"/>
+      <c r="G102" s="11" t="n"/>
+      <c r="H102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="11" t="n"/>
@@ -56302,7 +56418,8 @@
       <c r="D103" s="11" t="n"/>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
-      <c r="G103" s="14" t="n"/>
+      <c r="G103" s="11" t="n"/>
+      <c r="H103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="11" t="n"/>
@@ -56311,7 +56428,8 @@
       <c r="D104" s="11" t="n"/>
       <c r="E104" s="11" t="n"/>
       <c r="F104" s="11" t="n"/>
-      <c r="G104" s="14" t="n"/>
+      <c r="G104" s="11" t="n"/>
+      <c r="H104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="11" t="n"/>
@@ -56320,7 +56438,8 @@
       <c r="D105" s="11" t="n"/>
       <c r="E105" s="11" t="n"/>
       <c r="F105" s="11" t="n"/>
-      <c r="G105" s="14" t="n"/>
+      <c r="G105" s="11" t="n"/>
+      <c r="H105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="11" t="n"/>
@@ -56329,7 +56448,8 @@
       <c r="D106" s="11" t="n"/>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
-      <c r="G106" s="14" t="n"/>
+      <c r="G106" s="11" t="n"/>
+      <c r="H106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="11" t="n"/>
@@ -56338,7 +56458,8 @@
       <c r="D107" s="11" t="n"/>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
-      <c r="G107" s="14" t="n"/>
+      <c r="G107" s="11" t="n"/>
+      <c r="H107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="n"/>
@@ -56347,7 +56468,8 @@
       <c r="D108" s="11" t="n"/>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
-      <c r="G108" s="14" t="n"/>
+      <c r="G108" s="11" t="n"/>
+      <c r="H108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="11" t="n"/>
@@ -56356,7 +56478,8 @@
       <c r="D109" s="11" t="n"/>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
-      <c r="G109" s="14" t="n"/>
+      <c r="G109" s="11" t="n"/>
+      <c r="H109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="n"/>
@@ -56365,7 +56488,8 @@
       <c r="D110" s="11" t="n"/>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
-      <c r="G110" s="14" t="n"/>
+      <c r="G110" s="11" t="n"/>
+      <c r="H110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="11" t="n"/>
@@ -56374,7 +56498,8 @@
       <c r="D111" s="11" t="n"/>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
-      <c r="G111" s="14" t="n"/>
+      <c r="G111" s="11" t="n"/>
+      <c r="H111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="11" t="n"/>
@@ -56383,7 +56508,8 @@
       <c r="D112" s="11" t="n"/>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
-      <c r="G112" s="14" t="n"/>
+      <c r="G112" s="11" t="n"/>
+      <c r="H112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="11" t="n"/>
@@ -56392,7 +56518,8 @@
       <c r="D113" s="11" t="n"/>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
-      <c r="G113" s="14" t="n"/>
+      <c r="G113" s="11" t="n"/>
+      <c r="H113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="11" t="n"/>
@@ -56401,7 +56528,8 @@
       <c r="D114" s="11" t="n"/>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
-      <c r="G114" s="14" t="n"/>
+      <c r="G114" s="11" t="n"/>
+      <c r="H114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="11" t="n"/>
@@ -56410,7 +56538,8 @@
       <c r="D115" s="11" t="n"/>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
-      <c r="G115" s="14" t="n"/>
+      <c r="G115" s="11" t="n"/>
+      <c r="H115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="11" t="n"/>
@@ -56419,7 +56548,8 @@
       <c r="D116" s="11" t="n"/>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
-      <c r="G116" s="14" t="n"/>
+      <c r="G116" s="11" t="n"/>
+      <c r="H116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="11" t="n"/>
@@ -56428,7 +56558,8 @@
       <c r="D117" s="11" t="n"/>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
-      <c r="G117" s="14" t="n"/>
+      <c r="G117" s="11" t="n"/>
+      <c r="H117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="11" t="n"/>
@@ -56437,7 +56568,8 @@
       <c r="D118" s="11" t="n"/>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
-      <c r="G118" s="14" t="n"/>
+      <c r="G118" s="11" t="n"/>
+      <c r="H118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n"/>
@@ -56446,7 +56578,8 @@
       <c r="D119" s="11" t="n"/>
       <c r="E119" s="11" t="n"/>
       <c r="F119" s="11" t="n"/>
-      <c r="G119" s="14" t="n"/>
+      <c r="G119" s="11" t="n"/>
+      <c r="H119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="n"/>
@@ -56455,7 +56588,8 @@
       <c r="D120" s="11" t="n"/>
       <c r="E120" s="11" t="n"/>
       <c r="F120" s="11" t="n"/>
-      <c r="G120" s="14" t="n"/>
+      <c r="G120" s="11" t="n"/>
+      <c r="H120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="11" t="n"/>
@@ -56464,7 +56598,8 @@
       <c r="D121" s="11" t="n"/>
       <c r="E121" s="11" t="n"/>
       <c r="F121" s="11" t="n"/>
-      <c r="G121" s="14" t="n"/>
+      <c r="G121" s="11" t="n"/>
+      <c r="H121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="11" t="n"/>
@@ -56473,7 +56608,8 @@
       <c r="D122" s="11" t="n"/>
       <c r="E122" s="11" t="n"/>
       <c r="F122" s="11" t="n"/>
-      <c r="G122" s="14" t="n"/>
+      <c r="G122" s="11" t="n"/>
+      <c r="H122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="11" t="n"/>
@@ -56482,7 +56618,8 @@
       <c r="D123" s="11" t="n"/>
       <c r="E123" s="11" t="n"/>
       <c r="F123" s="11" t="n"/>
-      <c r="G123" s="14" t="n"/>
+      <c r="G123" s="11" t="n"/>
+      <c r="H123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="n"/>
@@ -56491,7 +56628,8 @@
       <c r="D124" s="11" t="n"/>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
-      <c r="G124" s="14" t="n"/>
+      <c r="G124" s="11" t="n"/>
+      <c r="H124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="11" t="n"/>
@@ -56500,7 +56638,8 @@
       <c r="D125" s="11" t="n"/>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
-      <c r="G125" s="14" t="n"/>
+      <c r="G125" s="11" t="n"/>
+      <c r="H125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="11" t="n"/>
@@ -56509,7 +56648,8 @@
       <c r="D126" s="11" t="n"/>
       <c r="E126" s="11" t="n"/>
       <c r="F126" s="11" t="n"/>
-      <c r="G126" s="14" t="n"/>
+      <c r="G126" s="11" t="n"/>
+      <c r="H126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="11" t="n"/>
@@ -56518,7 +56658,8 @@
       <c r="D127" s="11" t="n"/>
       <c r="E127" s="11" t="n"/>
       <c r="F127" s="11" t="n"/>
-      <c r="G127" s="14" t="n"/>
+      <c r="G127" s="11" t="n"/>
+      <c r="H127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="11" t="n"/>
@@ -56527,7 +56668,8 @@
       <c r="D128" s="11" t="n"/>
       <c r="E128" s="11" t="n"/>
       <c r="F128" s="11" t="n"/>
-      <c r="G128" s="14" t="n"/>
+      <c r="G128" s="11" t="n"/>
+      <c r="H128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="11" t="n"/>
@@ -56536,7 +56678,8 @@
       <c r="D129" s="11" t="n"/>
       <c r="E129" s="11" t="n"/>
       <c r="F129" s="11" t="n"/>
-      <c r="G129" s="14" t="n"/>
+      <c r="G129" s="11" t="n"/>
+      <c r="H129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="11" t="n"/>
@@ -56545,7 +56688,8 @@
       <c r="D130" s="11" t="n"/>
       <c r="E130" s="11" t="n"/>
       <c r="F130" s="11" t="n"/>
-      <c r="G130" s="14" t="n"/>
+      <c r="G130" s="11" t="n"/>
+      <c r="H130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="n"/>
@@ -56554,7 +56698,8 @@
       <c r="D131" s="11" t="n"/>
       <c r="E131" s="11" t="n"/>
       <c r="F131" s="11" t="n"/>
-      <c r="G131" s="14" t="n"/>
+      <c r="G131" s="11" t="n"/>
+      <c r="H131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="11" t="n"/>
@@ -56563,7 +56708,8 @@
       <c r="D132" s="11" t="n"/>
       <c r="E132" s="11" t="n"/>
       <c r="F132" s="11" t="n"/>
-      <c r="G132" s="14" t="n"/>
+      <c r="G132" s="11" t="n"/>
+      <c r="H132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="11" t="n"/>
@@ -56572,7 +56718,8 @@
       <c r="D133" s="11" t="n"/>
       <c r="E133" s="11" t="n"/>
       <c r="F133" s="11" t="n"/>
-      <c r="G133" s="14" t="n"/>
+      <c r="G133" s="11" t="n"/>
+      <c r="H133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="11" t="n"/>
@@ -56581,7 +56728,8 @@
       <c r="D134" s="11" t="n"/>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
-      <c r="G134" s="14" t="n"/>
+      <c r="G134" s="11" t="n"/>
+      <c r="H134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="11" t="n"/>
@@ -56590,7 +56738,8 @@
       <c r="D135" s="11" t="n"/>
       <c r="E135" s="11" t="n"/>
       <c r="F135" s="11" t="n"/>
-      <c r="G135" s="14" t="n"/>
+      <c r="G135" s="11" t="n"/>
+      <c r="H135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="11" t="n"/>
@@ -56599,7 +56748,8 @@
       <c r="D136" s="11" t="n"/>
       <c r="E136" s="11" t="n"/>
       <c r="F136" s="11" t="n"/>
-      <c r="G136" s="14" t="n"/>
+      <c r="G136" s="11" t="n"/>
+      <c r="H136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="11" t="n"/>
@@ -56608,7 +56758,8 @@
       <c r="D137" s="11" t="n"/>
       <c r="E137" s="11" t="n"/>
       <c r="F137" s="11" t="n"/>
-      <c r="G137" s="14" t="n"/>
+      <c r="G137" s="11" t="n"/>
+      <c r="H137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="11" t="n"/>
@@ -56617,7 +56768,8 @@
       <c r="D138" s="11" t="n"/>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
-      <c r="G138" s="14" t="n"/>
+      <c r="G138" s="11" t="n"/>
+      <c r="H138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="11" t="n"/>
@@ -56626,7 +56778,8 @@
       <c r="D139" s="11" t="n"/>
       <c r="E139" s="11" t="n"/>
       <c r="F139" s="11" t="n"/>
-      <c r="G139" s="14" t="n"/>
+      <c r="G139" s="11" t="n"/>
+      <c r="H139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="11" t="n"/>
@@ -56635,7 +56788,8 @@
       <c r="D140" s="11" t="n"/>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
-      <c r="G140" s="14" t="n"/>
+      <c r="G140" s="11" t="n"/>
+      <c r="H140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="11" t="n"/>
@@ -56644,7 +56798,8 @@
       <c r="D141" s="11" t="n"/>
       <c r="E141" s="11" t="n"/>
       <c r="F141" s="11" t="n"/>
-      <c r="G141" s="14" t="n"/>
+      <c r="G141" s="11" t="n"/>
+      <c r="H141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="11" t="n"/>
@@ -56653,7 +56808,8 @@
       <c r="D142" s="11" t="n"/>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
-      <c r="G142" s="14" t="n"/>
+      <c r="G142" s="11" t="n"/>
+      <c r="H142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="n"/>
@@ -56662,7 +56818,8 @@
       <c r="D143" s="11" t="n"/>
       <c r="E143" s="11" t="n"/>
       <c r="F143" s="11" t="n"/>
-      <c r="G143" s="14" t="n"/>
+      <c r="G143" s="11" t="n"/>
+      <c r="H143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="11" t="n"/>
@@ -56671,7 +56828,8 @@
       <c r="D144" s="11" t="n"/>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
-      <c r="G144" s="14" t="n"/>
+      <c r="G144" s="11" t="n"/>
+      <c r="H144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="n"/>
@@ -56680,7 +56838,8 @@
       <c r="D145" s="11" t="n"/>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
-      <c r="G145" s="14" t="n"/>
+      <c r="G145" s="11" t="n"/>
+      <c r="H145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="11" t="n"/>
@@ -56689,7 +56848,8 @@
       <c r="D146" s="11" t="n"/>
       <c r="E146" s="11" t="n"/>
       <c r="F146" s="11" t="n"/>
-      <c r="G146" s="14" t="n"/>
+      <c r="G146" s="11" t="n"/>
+      <c r="H146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="11" t="n"/>
@@ -56698,7 +56858,8 @@
       <c r="D147" s="11" t="n"/>
       <c r="E147" s="11" t="n"/>
       <c r="F147" s="11" t="n"/>
-      <c r="G147" s="14" t="n"/>
+      <c r="G147" s="11" t="n"/>
+      <c r="H147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="11" t="n"/>
@@ -56707,7 +56868,8 @@
       <c r="D148" s="11" t="n"/>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
-      <c r="G148" s="14" t="n"/>
+      <c r="G148" s="11" t="n"/>
+      <c r="H148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="11" t="n"/>
@@ -56716,7 +56878,8 @@
       <c r="D149" s="11" t="n"/>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
-      <c r="G149" s="14" t="n"/>
+      <c r="G149" s="11" t="n"/>
+      <c r="H149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="11" t="n"/>
@@ -56725,7 +56888,8 @@
       <c r="D150" s="11" t="n"/>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
-      <c r="G150" s="14" t="n"/>
+      <c r="G150" s="11" t="n"/>
+      <c r="H150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="11" t="n"/>
@@ -56734,7 +56898,8 @@
       <c r="D151" s="11" t="n"/>
       <c r="E151" s="11" t="n"/>
       <c r="F151" s="11" t="n"/>
-      <c r="G151" s="14" t="n"/>
+      <c r="G151" s="11" t="n"/>
+      <c r="H151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="11" t="n"/>
@@ -56743,7 +56908,8 @@
       <c r="D152" s="11" t="n"/>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
-      <c r="G152" s="14" t="n"/>
+      <c r="G152" s="11" t="n"/>
+      <c r="H152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="11" t="n"/>
@@ -56752,7 +56918,8 @@
       <c r="D153" s="11" t="n"/>
       <c r="E153" s="11" t="n"/>
       <c r="F153" s="11" t="n"/>
-      <c r="G153" s="14" t="n"/>
+      <c r="G153" s="11" t="n"/>
+      <c r="H153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="n"/>
@@ -56761,7 +56928,8 @@
       <c r="D154" s="11" t="n"/>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
-      <c r="G154" s="14" t="n"/>
+      <c r="G154" s="11" t="n"/>
+      <c r="H154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="11" t="n"/>
@@ -56770,7 +56938,8 @@
       <c r="D155" s="11" t="n"/>
       <c r="E155" s="11" t="n"/>
       <c r="F155" s="11" t="n"/>
-      <c r="G155" s="14" t="n"/>
+      <c r="G155" s="11" t="n"/>
+      <c r="H155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="11" t="n"/>
@@ -56779,7 +56948,8 @@
       <c r="D156" s="11" t="n"/>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
-      <c r="G156" s="14" t="n"/>
+      <c r="G156" s="11" t="n"/>
+      <c r="H156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="11" t="n"/>
@@ -56788,7 +56958,8 @@
       <c r="D157" s="11" t="n"/>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
-      <c r="G157" s="14" t="n"/>
+      <c r="G157" s="11" t="n"/>
+      <c r="H157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="11" t="n"/>
@@ -56797,7 +56968,8 @@
       <c r="D158" s="11" t="n"/>
       <c r="E158" s="11" t="n"/>
       <c r="F158" s="11" t="n"/>
-      <c r="G158" s="14" t="n"/>
+      <c r="G158" s="11" t="n"/>
+      <c r="H158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="11" t="n"/>
@@ -56806,7 +56978,8 @@
       <c r="D159" s="11" t="n"/>
       <c r="E159" s="11" t="n"/>
       <c r="F159" s="11" t="n"/>
-      <c r="G159" s="14" t="n"/>
+      <c r="G159" s="11" t="n"/>
+      <c r="H159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="11" t="n"/>
@@ -56815,7 +56988,8 @@
       <c r="D160" s="11" t="n"/>
       <c r="E160" s="11" t="n"/>
       <c r="F160" s="11" t="n"/>
-      <c r="G160" s="14" t="n"/>
+      <c r="G160" s="11" t="n"/>
+      <c r="H160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="11" t="n"/>
@@ -56824,7 +56998,8 @@
       <c r="D161" s="11" t="n"/>
       <c r="E161" s="11" t="n"/>
       <c r="F161" s="11" t="n"/>
-      <c r="G161" s="14" t="n"/>
+      <c r="G161" s="11" t="n"/>
+      <c r="H161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="11" t="n"/>
@@ -56833,7 +57008,8 @@
       <c r="D162" s="11" t="n"/>
       <c r="E162" s="11" t="n"/>
       <c r="F162" s="11" t="n"/>
-      <c r="G162" s="14" t="n"/>
+      <c r="G162" s="11" t="n"/>
+      <c r="H162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="n"/>
@@ -56842,7 +57018,8 @@
       <c r="D163" s="11" t="n"/>
       <c r="E163" s="11" t="n"/>
       <c r="F163" s="11" t="n"/>
-      <c r="G163" s="14" t="n"/>
+      <c r="G163" s="11" t="n"/>
+      <c r="H163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="11" t="n"/>
@@ -56851,7 +57028,8 @@
       <c r="D164" s="11" t="n"/>
       <c r="E164" s="11" t="n"/>
       <c r="F164" s="11" t="n"/>
-      <c r="G164" s="14" t="n"/>
+      <c r="G164" s="11" t="n"/>
+      <c r="H164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="11" t="n"/>
@@ -56860,7 +57038,8 @@
       <c r="D165" s="11" t="n"/>
       <c r="E165" s="11" t="n"/>
       <c r="F165" s="11" t="n"/>
-      <c r="G165" s="14" t="n"/>
+      <c r="G165" s="11" t="n"/>
+      <c r="H165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="11" t="n"/>
@@ -56869,7 +57048,8 @@
       <c r="D166" s="11" t="n"/>
       <c r="E166" s="11" t="n"/>
       <c r="F166" s="11" t="n"/>
-      <c r="G166" s="14" t="n"/>
+      <c r="G166" s="11" t="n"/>
+      <c r="H166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="11" t="n"/>
@@ -56878,7 +57058,8 @@
       <c r="D167" s="11" t="n"/>
       <c r="E167" s="11" t="n"/>
       <c r="F167" s="11" t="n"/>
-      <c r="G167" s="14" t="n"/>
+      <c r="G167" s="11" t="n"/>
+      <c r="H167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="11" t="n"/>
@@ -56887,7 +57068,8 @@
       <c r="D168" s="11" t="n"/>
       <c r="E168" s="11" t="n"/>
       <c r="F168" s="11" t="n"/>
-      <c r="G168" s="14" t="n"/>
+      <c r="G168" s="11" t="n"/>
+      <c r="H168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="11" t="n"/>
@@ -56896,7 +57078,8 @@
       <c r="D169" s="11" t="n"/>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
-      <c r="G169" s="14" t="n"/>
+      <c r="G169" s="11" t="n"/>
+      <c r="H169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="11" t="n"/>
@@ -56905,7 +57088,8 @@
       <c r="D170" s="11" t="n"/>
       <c r="E170" s="11" t="n"/>
       <c r="F170" s="11" t="n"/>
-      <c r="G170" s="14" t="n"/>
+      <c r="G170" s="11" t="n"/>
+      <c r="H170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="11" t="n"/>
@@ -56914,7 +57098,8 @@
       <c r="D171" s="11" t="n"/>
       <c r="E171" s="11" t="n"/>
       <c r="F171" s="11" t="n"/>
-      <c r="G171" s="14" t="n"/>
+      <c r="G171" s="11" t="n"/>
+      <c r="H171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="11" t="n"/>
@@ -56923,7 +57108,8 @@
       <c r="D172" s="11" t="n"/>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
-      <c r="G172" s="14" t="n"/>
+      <c r="G172" s="11" t="n"/>
+      <c r="H172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="11" t="n"/>
@@ -56932,7 +57118,8 @@
       <c r="D173" s="11" t="n"/>
       <c r="E173" s="11" t="n"/>
       <c r="F173" s="11" t="n"/>
-      <c r="G173" s="14" t="n"/>
+      <c r="G173" s="11" t="n"/>
+      <c r="H173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="11" t="n"/>
@@ -56941,7 +57128,8 @@
       <c r="D174" s="11" t="n"/>
       <c r="E174" s="11" t="n"/>
       <c r="F174" s="11" t="n"/>
-      <c r="G174" s="14" t="n"/>
+      <c r="G174" s="11" t="n"/>
+      <c r="H174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="11" t="n"/>
@@ -56950,7 +57138,8 @@
       <c r="D175" s="11" t="n"/>
       <c r="E175" s="11" t="n"/>
       <c r="F175" s="11" t="n"/>
-      <c r="G175" s="14" t="n"/>
+      <c r="G175" s="11" t="n"/>
+      <c r="H175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="n"/>
@@ -56959,7 +57148,8 @@
       <c r="D176" s="11" t="n"/>
       <c r="E176" s="11" t="n"/>
       <c r="F176" s="11" t="n"/>
-      <c r="G176" s="14" t="n"/>
+      <c r="G176" s="11" t="n"/>
+      <c r="H176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="11" t="n"/>
@@ -56968,7 +57158,8 @@
       <c r="D177" s="11" t="n"/>
       <c r="E177" s="11" t="n"/>
       <c r="F177" s="11" t="n"/>
-      <c r="G177" s="14" t="n"/>
+      <c r="G177" s="11" t="n"/>
+      <c r="H177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="11" t="n"/>
@@ -56977,7 +57168,8 @@
       <c r="D178" s="11" t="n"/>
       <c r="E178" s="11" t="n"/>
       <c r="F178" s="11" t="n"/>
-      <c r="G178" s="14" t="n"/>
+      <c r="G178" s="11" t="n"/>
+      <c r="H178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="11" t="n"/>
@@ -56986,7 +57178,8 @@
       <c r="D179" s="11" t="n"/>
       <c r="E179" s="11" t="n"/>
       <c r="F179" s="11" t="n"/>
-      <c r="G179" s="14" t="n"/>
+      <c r="G179" s="11" t="n"/>
+      <c r="H179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="11" t="n"/>
@@ -56995,7 +57188,8 @@
       <c r="D180" s="11" t="n"/>
       <c r="E180" s="11" t="n"/>
       <c r="F180" s="11" t="n"/>
-      <c r="G180" s="14" t="n"/>
+      <c r="G180" s="11" t="n"/>
+      <c r="H180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="11" t="n"/>
@@ -57004,7 +57198,8 @@
       <c r="D181" s="11" t="n"/>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
-      <c r="G181" s="14" t="n"/>
+      <c r="G181" s="11" t="n"/>
+      <c r="H181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="11" t="n"/>
@@ -57013,7 +57208,8 @@
       <c r="D182" s="11" t="n"/>
       <c r="E182" s="11" t="n"/>
       <c r="F182" s="11" t="n"/>
-      <c r="G182" s="14" t="n"/>
+      <c r="G182" s="11" t="n"/>
+      <c r="H182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="11" t="n"/>
@@ -57022,7 +57218,8 @@
       <c r="D183" s="11" t="n"/>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
-      <c r="G183" s="14" t="n"/>
+      <c r="G183" s="11" t="n"/>
+      <c r="H183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="11" t="n"/>
@@ -57031,7 +57228,8 @@
       <c r="D184" s="11" t="n"/>
       <c r="E184" s="11" t="n"/>
       <c r="F184" s="11" t="n"/>
-      <c r="G184" s="14" t="n"/>
+      <c r="G184" s="11" t="n"/>
+      <c r="H184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="11" t="n"/>
@@ -57040,7 +57238,8 @@
       <c r="D185" s="11" t="n"/>
       <c r="E185" s="11" t="n"/>
       <c r="F185" s="11" t="n"/>
-      <c r="G185" s="14" t="n"/>
+      <c r="G185" s="11" t="n"/>
+      <c r="H185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="11" t="n"/>
@@ -57049,7 +57248,8 @@
       <c r="D186" s="11" t="n"/>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
-      <c r="G186" s="14" t="n"/>
+      <c r="G186" s="11" t="n"/>
+      <c r="H186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="11" t="n"/>
@@ -57058,7 +57258,8 @@
       <c r="D187" s="11" t="n"/>
       <c r="E187" s="11" t="n"/>
       <c r="F187" s="11" t="n"/>
-      <c r="G187" s="14" t="n"/>
+      <c r="G187" s="11" t="n"/>
+      <c r="H187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="11" t="n"/>
@@ -57067,7 +57268,8 @@
       <c r="D188" s="11" t="n"/>
       <c r="E188" s="11" t="n"/>
       <c r="F188" s="11" t="n"/>
-      <c r="G188" s="14" t="n"/>
+      <c r="G188" s="11" t="n"/>
+      <c r="H188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="n"/>
@@ -57076,7 +57278,8 @@
       <c r="D189" s="11" t="n"/>
       <c r="E189" s="11" t="n"/>
       <c r="F189" s="11" t="n"/>
-      <c r="G189" s="14" t="n"/>
+      <c r="G189" s="11" t="n"/>
+      <c r="H189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="11" t="n"/>
@@ -57085,7 +57288,8 @@
       <c r="D190" s="11" t="n"/>
       <c r="E190" s="11" t="n"/>
       <c r="F190" s="11" t="n"/>
-      <c r="G190" s="14" t="n"/>
+      <c r="G190" s="11" t="n"/>
+      <c r="H190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="11" t="n"/>
@@ -57094,7 +57298,8 @@
       <c r="D191" s="11" t="n"/>
       <c r="E191" s="11" t="n"/>
       <c r="F191" s="11" t="n"/>
-      <c r="G191" s="14" t="n"/>
+      <c r="G191" s="11" t="n"/>
+      <c r="H191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="11" t="n"/>
@@ -57103,7 +57308,8 @@
       <c r="D192" s="11" t="n"/>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
-      <c r="G192" s="14" t="n"/>
+      <c r="G192" s="11" t="n"/>
+      <c r="H192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="11" t="n"/>
@@ -57112,7 +57318,8 @@
       <c r="D193" s="11" t="n"/>
       <c r="E193" s="11" t="n"/>
       <c r="F193" s="11" t="n"/>
-      <c r="G193" s="14" t="n"/>
+      <c r="G193" s="11" t="n"/>
+      <c r="H193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="11" t="n"/>
@@ -57121,7 +57328,8 @@
       <c r="D194" s="11" t="n"/>
       <c r="E194" s="11" t="n"/>
       <c r="F194" s="11" t="n"/>
-      <c r="G194" s="14" t="n"/>
+      <c r="G194" s="11" t="n"/>
+      <c r="H194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="11" t="n"/>
@@ -57130,7 +57338,8 @@
       <c r="D195" s="11" t="n"/>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
-      <c r="G195" s="14" t="n"/>
+      <c r="G195" s="11" t="n"/>
+      <c r="H195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="11" t="n"/>
@@ -57139,7 +57348,8 @@
       <c r="D196" s="11" t="n"/>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
-      <c r="G196" s="14" t="n"/>
+      <c r="G196" s="11" t="n"/>
+      <c r="H196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="11" t="n"/>
@@ -57148,7 +57358,8 @@
       <c r="D197" s="11" t="n"/>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
-      <c r="G197" s="14" t="n"/>
+      <c r="G197" s="11" t="n"/>
+      <c r="H197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="11" t="n"/>
@@ -57157,7 +57368,8 @@
       <c r="D198" s="11" t="n"/>
       <c r="E198" s="11" t="n"/>
       <c r="F198" s="11" t="n"/>
-      <c r="G198" s="14" t="n"/>
+      <c r="G198" s="11" t="n"/>
+      <c r="H198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="11" t="n"/>
@@ -57166,7 +57378,8 @@
       <c r="D199" s="11" t="n"/>
       <c r="E199" s="11" t="n"/>
       <c r="F199" s="11" t="n"/>
-      <c r="G199" s="14" t="n"/>
+      <c r="G199" s="11" t="n"/>
+      <c r="H199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="11" t="n"/>
@@ -57175,7 +57388,8 @@
       <c r="D200" s="11" t="n"/>
       <c r="E200" s="11" t="n"/>
       <c r="F200" s="11" t="n"/>
-      <c r="G200" s="14" t="n"/>
+      <c r="G200" s="11" t="n"/>
+      <c r="H200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="11" t="n"/>
@@ -57184,7 +57398,8 @@
       <c r="D201" s="11" t="n"/>
       <c r="E201" s="11" t="n"/>
       <c r="F201" s="11" t="n"/>
-      <c r="G201" s="14" t="n"/>
+      <c r="G201" s="11" t="n"/>
+      <c r="H201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="11" t="n"/>
@@ -57193,7 +57408,8 @@
       <c r="D202" s="11" t="n"/>
       <c r="E202" s="11" t="n"/>
       <c r="F202" s="11" t="n"/>
-      <c r="G202" s="14" t="n"/>
+      <c r="G202" s="11" t="n"/>
+      <c r="H202" s="14" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="11" t="n"/>
@@ -57202,7 +57418,8 @@
       <c r="D203" s="11" t="n"/>
       <c r="E203" s="11" t="n"/>
       <c r="F203" s="11" t="n"/>
-      <c r="G203" s="14" t="n"/>
+      <c r="G203" s="11" t="n"/>
+      <c r="H203" s="14" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="11" t="n"/>
@@ -57211,7 +57428,8 @@
       <c r="D204" s="11" t="n"/>
       <c r="E204" s="11" t="n"/>
       <c r="F204" s="11" t="n"/>
-      <c r="G204" s="14" t="n"/>
+      <c r="G204" s="11" t="n"/>
+      <c r="H204" s="14" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="11" t="n"/>
@@ -57220,7 +57438,8 @@
       <c r="D205" s="11" t="n"/>
       <c r="E205" s="11" t="n"/>
       <c r="F205" s="11" t="n"/>
-      <c r="G205" s="14" t="n"/>
+      <c r="G205" s="11" t="n"/>
+      <c r="H205" s="14" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="11" t="n"/>
@@ -57229,7 +57448,8 @@
       <c r="D206" s="11" t="n"/>
       <c r="E206" s="11" t="n"/>
       <c r="F206" s="11" t="n"/>
-      <c r="G206" s="14" t="n"/>
+      <c r="G206" s="11" t="n"/>
+      <c r="H206" s="14" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="11" t="n"/>
@@ -57238,7 +57458,8 @@
       <c r="D207" s="11" t="n"/>
       <c r="E207" s="11" t="n"/>
       <c r="F207" s="11" t="n"/>
-      <c r="G207" s="14" t="n"/>
+      <c r="G207" s="11" t="n"/>
+      <c r="H207" s="14" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="11" t="n"/>
@@ -57247,7 +57468,8 @@
       <c r="D208" s="11" t="n"/>
       <c r="E208" s="11" t="n"/>
       <c r="F208" s="11" t="n"/>
-      <c r="G208" s="14" t="n"/>
+      <c r="G208" s="11" t="n"/>
+      <c r="H208" s="14" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="11" t="n"/>
@@ -57256,7 +57478,8 @@
       <c r="D209" s="11" t="n"/>
       <c r="E209" s="11" t="n"/>
       <c r="F209" s="11" t="n"/>
-      <c r="G209" s="14" t="n"/>
+      <c r="G209" s="11" t="n"/>
+      <c r="H209" s="14" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="11" t="n"/>
@@ -57265,7 +57488,8 @@
       <c r="D210" s="11" t="n"/>
       <c r="E210" s="11" t="n"/>
       <c r="F210" s="11" t="n"/>
-      <c r="G210" s="14" t="n"/>
+      <c r="G210" s="11" t="n"/>
+      <c r="H210" s="14" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="11" t="n"/>
@@ -57274,7 +57498,8 @@
       <c r="D211" s="11" t="n"/>
       <c r="E211" s="11" t="n"/>
       <c r="F211" s="11" t="n"/>
-      <c r="G211" s="14" t="n"/>
+      <c r="G211" s="11" t="n"/>
+      <c r="H211" s="14" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="n"/>
@@ -57283,7 +57508,8 @@
       <c r="D212" s="11" t="n"/>
       <c r="E212" s="11" t="n"/>
       <c r="F212" s="11" t="n"/>
-      <c r="G212" s="14" t="n"/>
+      <c r="G212" s="11" t="n"/>
+      <c r="H212" s="14" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="11" t="n"/>
@@ -57292,7 +57518,8 @@
       <c r="D213" s="11" t="n"/>
       <c r="E213" s="11" t="n"/>
       <c r="F213" s="11" t="n"/>
-      <c r="G213" s="14" t="n"/>
+      <c r="G213" s="11" t="n"/>
+      <c r="H213" s="14" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="11" t="n"/>
@@ -57301,7 +57528,8 @@
       <c r="D214" s="11" t="n"/>
       <c r="E214" s="11" t="n"/>
       <c r="F214" s="11" t="n"/>
-      <c r="G214" s="14" t="n"/>
+      <c r="G214" s="11" t="n"/>
+      <c r="H214" s="14" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="11" t="n"/>
@@ -57310,7 +57538,8 @@
       <c r="D215" s="11" t="n"/>
       <c r="E215" s="11" t="n"/>
       <c r="F215" s="11" t="n"/>
-      <c r="G215" s="14" t="n"/>
+      <c r="G215" s="11" t="n"/>
+      <c r="H215" s="14" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="11" t="n"/>
@@ -57319,7 +57548,8 @@
       <c r="D216" s="11" t="n"/>
       <c r="E216" s="11" t="n"/>
       <c r="F216" s="11" t="n"/>
-      <c r="G216" s="14" t="n"/>
+      <c r="G216" s="11" t="n"/>
+      <c r="H216" s="14" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="11" t="n"/>
@@ -57328,7 +57558,8 @@
       <c r="D217" s="11" t="n"/>
       <c r="E217" s="11" t="n"/>
       <c r="F217" s="11" t="n"/>
-      <c r="G217" s="14" t="n"/>
+      <c r="G217" s="11" t="n"/>
+      <c r="H217" s="14" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="11" t="n"/>
@@ -57337,7 +57568,8 @@
       <c r="D218" s="11" t="n"/>
       <c r="E218" s="11" t="n"/>
       <c r="F218" s="11" t="n"/>
-      <c r="G218" s="14" t="n"/>
+      <c r="G218" s="11" t="n"/>
+      <c r="H218" s="14" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="11" t="n"/>
@@ -57346,7 +57578,8 @@
       <c r="D219" s="11" t="n"/>
       <c r="E219" s="11" t="n"/>
       <c r="F219" s="11" t="n"/>
-      <c r="G219" s="14" t="n"/>
+      <c r="G219" s="11" t="n"/>
+      <c r="H219" s="14" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="11" t="n"/>
@@ -57355,7 +57588,8 @@
       <c r="D220" s="11" t="n"/>
       <c r="E220" s="11" t="n"/>
       <c r="F220" s="11" t="n"/>
-      <c r="G220" s="14" t="n"/>
+      <c r="G220" s="11" t="n"/>
+      <c r="H220" s="14" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="n"/>
@@ -57364,7 +57598,8 @@
       <c r="D221" s="11" t="n"/>
       <c r="E221" s="11" t="n"/>
       <c r="F221" s="11" t="n"/>
-      <c r="G221" s="14" t="n"/>
+      <c r="G221" s="11" t="n"/>
+      <c r="H221" s="14" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="11" t="n"/>
@@ -57373,7 +57608,8 @@
       <c r="D222" s="11" t="n"/>
       <c r="E222" s="11" t="n"/>
       <c r="F222" s="11" t="n"/>
-      <c r="G222" s="14" t="n"/>
+      <c r="G222" s="11" t="n"/>
+      <c r="H222" s="14" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="11" t="n"/>
@@ -57382,7 +57618,8 @@
       <c r="D223" s="11" t="n"/>
       <c r="E223" s="11" t="n"/>
       <c r="F223" s="11" t="n"/>
-      <c r="G223" s="14" t="n"/>
+      <c r="G223" s="11" t="n"/>
+      <c r="H223" s="14" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="11" t="n"/>
@@ -57391,7 +57628,8 @@
       <c r="D224" s="11" t="n"/>
       <c r="E224" s="11" t="n"/>
       <c r="F224" s="11" t="n"/>
-      <c r="G224" s="14" t="n"/>
+      <c r="G224" s="11" t="n"/>
+      <c r="H224" s="14" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="11" t="n"/>
@@ -57400,7 +57638,8 @@
       <c r="D225" s="11" t="n"/>
       <c r="E225" s="11" t="n"/>
       <c r="F225" s="11" t="n"/>
-      <c r="G225" s="14" t="n"/>
+      <c r="G225" s="11" t="n"/>
+      <c r="H225" s="14" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="11" t="n"/>
@@ -57409,7 +57648,8 @@
       <c r="D226" s="11" t="n"/>
       <c r="E226" s="11" t="n"/>
       <c r="F226" s="11" t="n"/>
-      <c r="G226" s="14" t="n"/>
+      <c r="G226" s="11" t="n"/>
+      <c r="H226" s="14" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="11" t="n"/>
@@ -57418,7 +57658,8 @@
       <c r="D227" s="11" t="n"/>
       <c r="E227" s="11" t="n"/>
       <c r="F227" s="11" t="n"/>
-      <c r="G227" s="14" t="n"/>
+      <c r="G227" s="11" t="n"/>
+      <c r="H227" s="14" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="11" t="n"/>
@@ -57427,7 +57668,8 @@
       <c r="D228" s="11" t="n"/>
       <c r="E228" s="11" t="n"/>
       <c r="F228" s="11" t="n"/>
-      <c r="G228" s="14" t="n"/>
+      <c r="G228" s="11" t="n"/>
+      <c r="H228" s="14" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="11" t="n"/>
@@ -57436,7 +57678,8 @@
       <c r="D229" s="11" t="n"/>
       <c r="E229" s="11" t="n"/>
       <c r="F229" s="11" t="n"/>
-      <c r="G229" s="14" t="n"/>
+      <c r="G229" s="11" t="n"/>
+      <c r="H229" s="14" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="11" t="n"/>
@@ -57445,7 +57688,8 @@
       <c r="D230" s="11" t="n"/>
       <c r="E230" s="11" t="n"/>
       <c r="F230" s="11" t="n"/>
-      <c r="G230" s="14" t="n"/>
+      <c r="G230" s="11" t="n"/>
+      <c r="H230" s="14" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="11" t="n"/>
@@ -57454,7 +57698,8 @@
       <c r="D231" s="11" t="n"/>
       <c r="E231" s="11" t="n"/>
       <c r="F231" s="11" t="n"/>
-      <c r="G231" s="14" t="n"/>
+      <c r="G231" s="11" t="n"/>
+      <c r="H231" s="14" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="11" t="n"/>
@@ -57463,7 +57708,8 @@
       <c r="D232" s="11" t="n"/>
       <c r="E232" s="11" t="n"/>
       <c r="F232" s="11" t="n"/>
-      <c r="G232" s="14" t="n"/>
+      <c r="G232" s="11" t="n"/>
+      <c r="H232" s="14" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="11" t="n"/>
@@ -57472,7 +57718,8 @@
       <c r="D233" s="11" t="n"/>
       <c r="E233" s="11" t="n"/>
       <c r="F233" s="11" t="n"/>
-      <c r="G233" s="14" t="n"/>
+      <c r="G233" s="11" t="n"/>
+      <c r="H233" s="14" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="n"/>
@@ -57481,7 +57728,8 @@
       <c r="D234" s="11" t="n"/>
       <c r="E234" s="11" t="n"/>
       <c r="F234" s="11" t="n"/>
-      <c r="G234" s="14" t="n"/>
+      <c r="G234" s="11" t="n"/>
+      <c r="H234" s="14" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="11" t="n"/>
@@ -57490,7 +57738,8 @@
       <c r="D235" s="11" t="n"/>
       <c r="E235" s="11" t="n"/>
       <c r="F235" s="11" t="n"/>
-      <c r="G235" s="14" t="n"/>
+      <c r="G235" s="11" t="n"/>
+      <c r="H235" s="14" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="11" t="n"/>
@@ -57499,7 +57748,8 @@
       <c r="D236" s="11" t="n"/>
       <c r="E236" s="11" t="n"/>
       <c r="F236" s="11" t="n"/>
-      <c r="G236" s="14" t="n"/>
+      <c r="G236" s="11" t="n"/>
+      <c r="H236" s="14" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="11" t="n"/>
@@ -57508,7 +57758,8 @@
       <c r="D237" s="11" t="n"/>
       <c r="E237" s="11" t="n"/>
       <c r="F237" s="11" t="n"/>
-      <c r="G237" s="14" t="n"/>
+      <c r="G237" s="11" t="n"/>
+      <c r="H237" s="14" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="11" t="n"/>
@@ -57517,7 +57768,8 @@
       <c r="D238" s="11" t="n"/>
       <c r="E238" s="11" t="n"/>
       <c r="F238" s="11" t="n"/>
-      <c r="G238" s="14" t="n"/>
+      <c r="G238" s="11" t="n"/>
+      <c r="H238" s="14" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="11" t="n"/>
@@ -57526,7 +57778,8 @@
       <c r="D239" s="11" t="n"/>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
-      <c r="G239" s="14" t="n"/>
+      <c r="G239" s="11" t="n"/>
+      <c r="H239" s="14" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="11" t="n"/>
@@ -57535,7 +57788,8 @@
       <c r="D240" s="11" t="n"/>
       <c r="E240" s="11" t="n"/>
       <c r="F240" s="11" t="n"/>
-      <c r="G240" s="14" t="n"/>
+      <c r="G240" s="11" t="n"/>
+      <c r="H240" s="14" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="11" t="n"/>
@@ -57544,7 +57798,8 @@
       <c r="D241" s="11" t="n"/>
       <c r="E241" s="11" t="n"/>
       <c r="F241" s="11" t="n"/>
-      <c r="G241" s="14" t="n"/>
+      <c r="G241" s="11" t="n"/>
+      <c r="H241" s="14" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="11" t="n"/>
@@ -57553,7 +57808,8 @@
       <c r="D242" s="11" t="n"/>
       <c r="E242" s="11" t="n"/>
       <c r="F242" s="11" t="n"/>
-      <c r="G242" s="14" t="n"/>
+      <c r="G242" s="11" t="n"/>
+      <c r="H242" s="14" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="11" t="n"/>
@@ -57562,7 +57818,8 @@
       <c r="D243" s="11" t="n"/>
       <c r="E243" s="11" t="n"/>
       <c r="F243" s="11" t="n"/>
-      <c r="G243" s="14" t="n"/>
+      <c r="G243" s="11" t="n"/>
+      <c r="H243" s="14" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="n"/>
@@ -57571,7 +57828,8 @@
       <c r="D244" s="11" t="n"/>
       <c r="E244" s="11" t="n"/>
       <c r="F244" s="11" t="n"/>
-      <c r="G244" s="14" t="n"/>
+      <c r="G244" s="11" t="n"/>
+      <c r="H244" s="14" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="11" t="n"/>
@@ -57580,7 +57838,8 @@
       <c r="D245" s="11" t="n"/>
       <c r="E245" s="11" t="n"/>
       <c r="F245" s="11" t="n"/>
-      <c r="G245" s="14" t="n"/>
+      <c r="G245" s="11" t="n"/>
+      <c r="H245" s="14" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="11" t="n"/>
@@ -57589,7 +57848,8 @@
       <c r="D246" s="11" t="n"/>
       <c r="E246" s="11" t="n"/>
       <c r="F246" s="11" t="n"/>
-      <c r="G246" s="14" t="n"/>
+      <c r="G246" s="11" t="n"/>
+      <c r="H246" s="14" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="11" t="n"/>
@@ -57598,7 +57858,8 @@
       <c r="D247" s="11" t="n"/>
       <c r="E247" s="11" t="n"/>
       <c r="F247" s="11" t="n"/>
-      <c r="G247" s="14" t="n"/>
+      <c r="G247" s="11" t="n"/>
+      <c r="H247" s="14" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="11" t="n"/>
@@ -57607,7 +57868,8 @@
       <c r="D248" s="11" t="n"/>
       <c r="E248" s="11" t="n"/>
       <c r="F248" s="11" t="n"/>
-      <c r="G248" s="14" t="n"/>
+      <c r="G248" s="11" t="n"/>
+      <c r="H248" s="14" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="11" t="n"/>
@@ -57616,7 +57878,8 @@
       <c r="D249" s="11" t="n"/>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
-      <c r="G249" s="14" t="n"/>
+      <c r="G249" s="11" t="n"/>
+      <c r="H249" s="14" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="11" t="n"/>
@@ -57625,7 +57888,8 @@
       <c r="D250" s="11" t="n"/>
       <c r="E250" s="11" t="n"/>
       <c r="F250" s="11" t="n"/>
-      <c r="G250" s="14" t="n"/>
+      <c r="G250" s="11" t="n"/>
+      <c r="H250" s="14" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="11" t="n"/>
@@ -57634,7 +57898,8 @@
       <c r="D251" s="11" t="n"/>
       <c r="E251" s="11" t="n"/>
       <c r="F251" s="11" t="n"/>
-      <c r="G251" s="14" t="n"/>
+      <c r="G251" s="11" t="n"/>
+      <c r="H251" s="14" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="11" t="n"/>
@@ -57643,7 +57908,8 @@
       <c r="D252" s="11" t="n"/>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
-      <c r="G252" s="14" t="n"/>
+      <c r="G252" s="11" t="n"/>
+      <c r="H252" s="14" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="11" t="n"/>
@@ -57652,7 +57918,8 @@
       <c r="D253" s="11" t="n"/>
       <c r="E253" s="11" t="n"/>
       <c r="F253" s="11" t="n"/>
-      <c r="G253" s="14" t="n"/>
+      <c r="G253" s="11" t="n"/>
+      <c r="H253" s="14" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="11" t="n"/>
@@ -57661,7 +57928,8 @@
       <c r="D254" s="11" t="n"/>
       <c r="E254" s="11" t="n"/>
       <c r="F254" s="11" t="n"/>
-      <c r="G254" s="14" t="n"/>
+      <c r="G254" s="11" t="n"/>
+      <c r="H254" s="14" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="n"/>
@@ -57670,7 +57938,8 @@
       <c r="D255" s="11" t="n"/>
       <c r="E255" s="11" t="n"/>
       <c r="F255" s="11" t="n"/>
-      <c r="G255" s="14" t="n"/>
+      <c r="G255" s="11" t="n"/>
+      <c r="H255" s="14" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="11" t="n"/>
@@ -57679,7 +57948,8 @@
       <c r="D256" s="11" t="n"/>
       <c r="E256" s="11" t="n"/>
       <c r="F256" s="11" t="n"/>
-      <c r="G256" s="14" t="n"/>
+      <c r="G256" s="11" t="n"/>
+      <c r="H256" s="14" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="11" t="n"/>
@@ -57688,7 +57958,8 @@
       <c r="D257" s="11" t="n"/>
       <c r="E257" s="11" t="n"/>
       <c r="F257" s="11" t="n"/>
-      <c r="G257" s="14" t="n"/>
+      <c r="G257" s="11" t="n"/>
+      <c r="H257" s="14" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="11" t="n"/>
@@ -57697,7 +57968,8 @@
       <c r="D258" s="11" t="n"/>
       <c r="E258" s="11" t="n"/>
       <c r="F258" s="11" t="n"/>
-      <c r="G258" s="14" t="n"/>
+      <c r="G258" s="11" t="n"/>
+      <c r="H258" s="14" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="11" t="n"/>
@@ -57706,7 +57978,8 @@
       <c r="D259" s="11" t="n"/>
       <c r="E259" s="11" t="n"/>
       <c r="F259" s="11" t="n"/>
-      <c r="G259" s="14" t="n"/>
+      <c r="G259" s="11" t="n"/>
+      <c r="H259" s="14" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="11" t="n"/>
@@ -57715,7 +57988,8 @@
       <c r="D260" s="11" t="n"/>
       <c r="E260" s="11" t="n"/>
       <c r="F260" s="11" t="n"/>
-      <c r="G260" s="14" t="n"/>
+      <c r="G260" s="11" t="n"/>
+      <c r="H260" s="14" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="11" t="n"/>
@@ -57724,7 +57998,8 @@
       <c r="D261" s="11" t="n"/>
       <c r="E261" s="11" t="n"/>
       <c r="F261" s="11" t="n"/>
-      <c r="G261" s="14" t="n"/>
+      <c r="G261" s="11" t="n"/>
+      <c r="H261" s="14" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="11" t="n"/>
@@ -57733,7 +58008,8 @@
       <c r="D262" s="11" t="n"/>
       <c r="E262" s="11" t="n"/>
       <c r="F262" s="11" t="n"/>
-      <c r="G262" s="14" t="n"/>
+      <c r="G262" s="11" t="n"/>
+      <c r="H262" s="14" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="11" t="n"/>
@@ -57742,7 +58018,8 @@
       <c r="D263" s="11" t="n"/>
       <c r="E263" s="11" t="n"/>
       <c r="F263" s="11" t="n"/>
-      <c r="G263" s="14" t="n"/>
+      <c r="G263" s="11" t="n"/>
+      <c r="H263" s="14" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="n"/>
@@ -57751,7 +58028,8 @@
       <c r="D264" s="11" t="n"/>
       <c r="E264" s="11" t="n"/>
       <c r="F264" s="11" t="n"/>
-      <c r="G264" s="14" t="n"/>
+      <c r="G264" s="11" t="n"/>
+      <c r="H264" s="14" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="11" t="n"/>
@@ -57760,7 +58038,8 @@
       <c r="D265" s="11" t="n"/>
       <c r="E265" s="11" t="n"/>
       <c r="F265" s="11" t="n"/>
-      <c r="G265" s="14" t="n"/>
+      <c r="G265" s="11" t="n"/>
+      <c r="H265" s="14" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="11" t="n"/>
@@ -57769,7 +58048,8 @@
       <c r="D266" s="11" t="n"/>
       <c r="E266" s="11" t="n"/>
       <c r="F266" s="11" t="n"/>
-      <c r="G266" s="14" t="n"/>
+      <c r="G266" s="11" t="n"/>
+      <c r="H266" s="14" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="11" t="n"/>
@@ -57778,7 +58058,8 @@
       <c r="D267" s="11" t="n"/>
       <c r="E267" s="11" t="n"/>
       <c r="F267" s="11" t="n"/>
-      <c r="G267" s="14" t="n"/>
+      <c r="G267" s="11" t="n"/>
+      <c r="H267" s="14" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="11" t="n"/>
@@ -57787,7 +58068,8 @@
       <c r="D268" s="11" t="n"/>
       <c r="E268" s="11" t="n"/>
       <c r="F268" s="11" t="n"/>
-      <c r="G268" s="14" t="n"/>
+      <c r="G268" s="11" t="n"/>
+      <c r="H268" s="14" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="11" t="n"/>
@@ -57796,7 +58078,8 @@
       <c r="D269" s="11" t="n"/>
       <c r="E269" s="11" t="n"/>
       <c r="F269" s="11" t="n"/>
-      <c r="G269" s="14" t="n"/>
+      <c r="G269" s="11" t="n"/>
+      <c r="H269" s="14" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="11" t="n"/>
@@ -57805,7 +58088,8 @@
       <c r="D270" s="11" t="n"/>
       <c r="E270" s="11" t="n"/>
       <c r="F270" s="11" t="n"/>
-      <c r="G270" s="14" t="n"/>
+      <c r="G270" s="11" t="n"/>
+      <c r="H270" s="14" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="11" t="n"/>
@@ -57814,7 +58098,8 @@
       <c r="D271" s="11" t="n"/>
       <c r="E271" s="11" t="n"/>
       <c r="F271" s="11" t="n"/>
-      <c r="G271" s="14" t="n"/>
+      <c r="G271" s="11" t="n"/>
+      <c r="H271" s="14" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="11" t="n"/>
@@ -57823,7 +58108,8 @@
       <c r="D272" s="11" t="n"/>
       <c r="E272" s="11" t="n"/>
       <c r="F272" s="11" t="n"/>
-      <c r="G272" s="14" t="n"/>
+      <c r="G272" s="11" t="n"/>
+      <c r="H272" s="14" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="11" t="n"/>
@@ -57832,7 +58118,8 @@
       <c r="D273" s="11" t="n"/>
       <c r="E273" s="11" t="n"/>
       <c r="F273" s="11" t="n"/>
-      <c r="G273" s="14" t="n"/>
+      <c r="G273" s="11" t="n"/>
+      <c r="H273" s="14" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="11" t="n"/>
@@ -57841,7 +58128,8 @@
       <c r="D274" s="11" t="n"/>
       <c r="E274" s="11" t="n"/>
       <c r="F274" s="11" t="n"/>
-      <c r="G274" s="14" t="n"/>
+      <c r="G274" s="11" t="n"/>
+      <c r="H274" s="14" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="11" t="n"/>
@@ -57850,7 +58138,8 @@
       <c r="D275" s="11" t="n"/>
       <c r="E275" s="11" t="n"/>
       <c r="F275" s="11" t="n"/>
-      <c r="G275" s="14" t="n"/>
+      <c r="G275" s="11" t="n"/>
+      <c r="H275" s="14" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="n"/>
@@ -57859,7 +58148,8 @@
       <c r="D276" s="11" t="n"/>
       <c r="E276" s="11" t="n"/>
       <c r="F276" s="11" t="n"/>
-      <c r="G276" s="14" t="n"/>
+      <c r="G276" s="11" t="n"/>
+      <c r="H276" s="14" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="11" t="n"/>
@@ -57868,7 +58158,8 @@
       <c r="D277" s="11" t="n"/>
       <c r="E277" s="11" t="n"/>
       <c r="F277" s="11" t="n"/>
-      <c r="G277" s="14" t="n"/>
+      <c r="G277" s="11" t="n"/>
+      <c r="H277" s="14" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="11" t="n"/>
@@ -57877,7 +58168,8 @@
       <c r="D278" s="11" t="n"/>
       <c r="E278" s="11" t="n"/>
       <c r="F278" s="11" t="n"/>
-      <c r="G278" s="14" t="n"/>
+      <c r="G278" s="11" t="n"/>
+      <c r="H278" s="14" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="11" t="n"/>
@@ -57886,7 +58178,8 @@
       <c r="D279" s="11" t="n"/>
       <c r="E279" s="11" t="n"/>
       <c r="F279" s="11" t="n"/>
-      <c r="G279" s="14" t="n"/>
+      <c r="G279" s="11" t="n"/>
+      <c r="H279" s="14" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="11" t="n"/>
@@ -57895,7 +58188,8 @@
       <c r="D280" s="11" t="n"/>
       <c r="E280" s="11" t="n"/>
       <c r="F280" s="11" t="n"/>
-      <c r="G280" s="14" t="n"/>
+      <c r="G280" s="11" t="n"/>
+      <c r="H280" s="14" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="11" t="n"/>
@@ -57904,7 +58198,8 @@
       <c r="D281" s="11" t="n"/>
       <c r="E281" s="11" t="n"/>
       <c r="F281" s="11" t="n"/>
-      <c r="G281" s="14" t="n"/>
+      <c r="G281" s="11" t="n"/>
+      <c r="H281" s="14" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="11" t="n"/>
@@ -57913,7 +58208,8 @@
       <c r="D282" s="11" t="n"/>
       <c r="E282" s="11" t="n"/>
       <c r="F282" s="11" t="n"/>
-      <c r="G282" s="14" t="n"/>
+      <c r="G282" s="11" t="n"/>
+      <c r="H282" s="14" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="11" t="n"/>
@@ -57922,7 +58218,8 @@
       <c r="D283" s="11" t="n"/>
       <c r="E283" s="11" t="n"/>
       <c r="F283" s="11" t="n"/>
-      <c r="G283" s="14" t="n"/>
+      <c r="G283" s="11" t="n"/>
+      <c r="H283" s="14" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="11" t="n"/>
@@ -57931,7 +58228,8 @@
       <c r="D284" s="11" t="n"/>
       <c r="E284" s="11" t="n"/>
       <c r="F284" s="11" t="n"/>
-      <c r="G284" s="14" t="n"/>
+      <c r="G284" s="11" t="n"/>
+      <c r="H284" s="14" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="11" t="n"/>
@@ -57940,7 +58238,8 @@
       <c r="D285" s="11" t="n"/>
       <c r="E285" s="11" t="n"/>
       <c r="F285" s="11" t="n"/>
-      <c r="G285" s="14" t="n"/>
+      <c r="G285" s="11" t="n"/>
+      <c r="H285" s="14" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="n"/>
@@ -57949,7 +58248,8 @@
       <c r="D286" s="11" t="n"/>
       <c r="E286" s="11" t="n"/>
       <c r="F286" s="11" t="n"/>
-      <c r="G286" s="14" t="n"/>
+      <c r="G286" s="11" t="n"/>
+      <c r="H286" s="14" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="11" t="n"/>
@@ -57958,7 +58258,8 @@
       <c r="D287" s="11" t="n"/>
       <c r="E287" s="11" t="n"/>
       <c r="F287" s="11" t="n"/>
-      <c r="G287" s="14" t="n"/>
+      <c r="G287" s="11" t="n"/>
+      <c r="H287" s="14" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="11" t="n"/>
@@ -57967,7 +58268,8 @@
       <c r="D288" s="11" t="n"/>
       <c r="E288" s="11" t="n"/>
       <c r="F288" s="11" t="n"/>
-      <c r="G288" s="14" t="n"/>
+      <c r="G288" s="11" t="n"/>
+      <c r="H288" s="14" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="11" t="n"/>
@@ -57976,7 +58278,8 @@
       <c r="D289" s="11" t="n"/>
       <c r="E289" s="11" t="n"/>
       <c r="F289" s="11" t="n"/>
-      <c r="G289" s="14" t="n"/>
+      <c r="G289" s="11" t="n"/>
+      <c r="H289" s="14" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="11" t="n"/>
@@ -57985,7 +58288,8 @@
       <c r="D290" s="11" t="n"/>
       <c r="E290" s="11" t="n"/>
       <c r="F290" s="11" t="n"/>
-      <c r="G290" s="14" t="n"/>
+      <c r="G290" s="11" t="n"/>
+      <c r="H290" s="14" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="11" t="n"/>
@@ -57994,7 +58298,8 @@
       <c r="D291" s="11" t="n"/>
       <c r="E291" s="11" t="n"/>
       <c r="F291" s="11" t="n"/>
-      <c r="G291" s="14" t="n"/>
+      <c r="G291" s="11" t="n"/>
+      <c r="H291" s="14" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="11" t="n"/>
@@ -58003,7 +58308,8 @@
       <c r="D292" s="11" t="n"/>
       <c r="E292" s="11" t="n"/>
       <c r="F292" s="11" t="n"/>
-      <c r="G292" s="14" t="n"/>
+      <c r="G292" s="11" t="n"/>
+      <c r="H292" s="14" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="11" t="n"/>
@@ -58012,7 +58318,8 @@
       <c r="D293" s="11" t="n"/>
       <c r="E293" s="11" t="n"/>
       <c r="F293" s="11" t="n"/>
-      <c r="G293" s="14" t="n"/>
+      <c r="G293" s="11" t="n"/>
+      <c r="H293" s="14" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="11" t="n"/>
@@ -58021,7 +58328,8 @@
       <c r="D294" s="11" t="n"/>
       <c r="E294" s="11" t="n"/>
       <c r="F294" s="11" t="n"/>
-      <c r="G294" s="14" t="n"/>
+      <c r="G294" s="11" t="n"/>
+      <c r="H294" s="14" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="11" t="n"/>
@@ -58030,7 +58338,8 @@
       <c r="D295" s="11" t="n"/>
       <c r="E295" s="11" t="n"/>
       <c r="F295" s="11" t="n"/>
-      <c r="G295" s="14" t="n"/>
+      <c r="G295" s="11" t="n"/>
+      <c r="H295" s="14" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="11" t="n"/>
@@ -58039,7 +58348,8 @@
       <c r="D296" s="11" t="n"/>
       <c r="E296" s="11" t="n"/>
       <c r="F296" s="11" t="n"/>
-      <c r="G296" s="14" t="n"/>
+      <c r="G296" s="11" t="n"/>
+      <c r="H296" s="14" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="11" t="n"/>
@@ -58048,7 +58358,8 @@
       <c r="D297" s="11" t="n"/>
       <c r="E297" s="11" t="n"/>
       <c r="F297" s="11" t="n"/>
-      <c r="G297" s="14" t="n"/>
+      <c r="G297" s="11" t="n"/>
+      <c r="H297" s="14" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="11" t="n"/>
@@ -58057,7 +58368,8 @@
       <c r="D298" s="11" t="n"/>
       <c r="E298" s="11" t="n"/>
       <c r="F298" s="11" t="n"/>
-      <c r="G298" s="14" t="n"/>
+      <c r="G298" s="11" t="n"/>
+      <c r="H298" s="14" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="11" t="n"/>
@@ -58066,7 +58378,8 @@
       <c r="D299" s="11" t="n"/>
       <c r="E299" s="11" t="n"/>
       <c r="F299" s="11" t="n"/>
-      <c r="G299" s="14" t="n"/>
+      <c r="G299" s="11" t="n"/>
+      <c r="H299" s="14" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="11" t="n"/>
@@ -58075,7 +58388,8 @@
       <c r="D300" s="11" t="n"/>
       <c r="E300" s="11" t="n"/>
       <c r="F300" s="11" t="n"/>
-      <c r="G300" s="14" t="n"/>
+      <c r="G300" s="11" t="n"/>
+      <c r="H300" s="14" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="11" t="n"/>
@@ -58084,7 +58398,8 @@
       <c r="D301" s="11" t="n"/>
       <c r="E301" s="11" t="n"/>
       <c r="F301" s="11" t="n"/>
-      <c r="G301" s="14" t="n"/>
+      <c r="G301" s="11" t="n"/>
+      <c r="H301" s="14" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="11" t="n"/>
@@ -58093,7 +58408,8 @@
       <c r="D302" s="11" t="n"/>
       <c r="E302" s="11" t="n"/>
       <c r="F302" s="11" t="n"/>
-      <c r="G302" s="14" t="n"/>
+      <c r="G302" s="11" t="n"/>
+      <c r="H302" s="14" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="11" t="n"/>
@@ -58102,7 +58418,8 @@
       <c r="D303" s="11" t="n"/>
       <c r="E303" s="11" t="n"/>
       <c r="F303" s="11" t="n"/>
-      <c r="G303" s="14" t="n"/>
+      <c r="G303" s="11" t="n"/>
+      <c r="H303" s="14" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="11" t="n"/>
@@ -58111,7 +58428,8 @@
       <c r="D304" s="11" t="n"/>
       <c r="E304" s="11" t="n"/>
       <c r="F304" s="11" t="n"/>
-      <c r="G304" s="14" t="n"/>
+      <c r="G304" s="11" t="n"/>
+      <c r="H304" s="14" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="n"/>
@@ -58120,7 +58438,8 @@
       <c r="D305" s="11" t="n"/>
       <c r="E305" s="11" t="n"/>
       <c r="F305" s="11" t="n"/>
-      <c r="G305" s="14" t="n"/>
+      <c r="G305" s="11" t="n"/>
+      <c r="H305" s="14" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="11" t="n"/>
@@ -58129,7 +58448,8 @@
       <c r="D306" s="11" t="n"/>
       <c r="E306" s="11" t="n"/>
       <c r="F306" s="11" t="n"/>
-      <c r="G306" s="14" t="n"/>
+      <c r="G306" s="11" t="n"/>
+      <c r="H306" s="14" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="11" t="n"/>
@@ -58138,7 +58458,8 @@
       <c r="D307" s="11" t="n"/>
       <c r="E307" s="11" t="n"/>
       <c r="F307" s="11" t="n"/>
-      <c r="G307" s="14" t="n"/>
+      <c r="G307" s="11" t="n"/>
+      <c r="H307" s="14" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="11" t="n"/>
@@ -58147,7 +58468,8 @@
       <c r="D308" s="11" t="n"/>
       <c r="E308" s="11" t="n"/>
       <c r="F308" s="11" t="n"/>
-      <c r="G308" s="14" t="n"/>
+      <c r="G308" s="11" t="n"/>
+      <c r="H308" s="14" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="11" t="n"/>
@@ -58156,7 +58478,8 @@
       <c r="D309" s="11" t="n"/>
       <c r="E309" s="11" t="n"/>
       <c r="F309" s="11" t="n"/>
-      <c r="G309" s="14" t="n"/>
+      <c r="G309" s="11" t="n"/>
+      <c r="H309" s="14" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="11" t="n"/>
@@ -58165,7 +58488,8 @@
       <c r="D310" s="11" t="n"/>
       <c r="E310" s="11" t="n"/>
       <c r="F310" s="11" t="n"/>
-      <c r="G310" s="14" t="n"/>
+      <c r="G310" s="11" t="n"/>
+      <c r="H310" s="14" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="11" t="n"/>
@@ -58174,7 +58498,8 @@
       <c r="D311" s="11" t="n"/>
       <c r="E311" s="11" t="n"/>
       <c r="F311" s="11" t="n"/>
-      <c r="G311" s="14" t="n"/>
+      <c r="G311" s="11" t="n"/>
+      <c r="H311" s="14" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="11" t="n"/>
@@ -58183,7 +58508,8 @@
       <c r="D312" s="11" t="n"/>
       <c r="E312" s="11" t="n"/>
       <c r="F312" s="11" t="n"/>
-      <c r="G312" s="14" t="n"/>
+      <c r="G312" s="11" t="n"/>
+      <c r="H312" s="14" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="11" t="n"/>
@@ -58192,7 +58518,8 @@
       <c r="D313" s="11" t="n"/>
       <c r="E313" s="11" t="n"/>
       <c r="F313" s="11" t="n"/>
-      <c r="G313" s="14" t="n"/>
+      <c r="G313" s="11" t="n"/>
+      <c r="H313" s="14" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="11" t="n"/>
@@ -58201,7 +58528,8 @@
       <c r="D314" s="11" t="n"/>
       <c r="E314" s="11" t="n"/>
       <c r="F314" s="11" t="n"/>
-      <c r="G314" s="14" t="n"/>
+      <c r="G314" s="11" t="n"/>
+      <c r="H314" s="14" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="11" t="n"/>
@@ -58210,7 +58538,8 @@
       <c r="D315" s="11" t="n"/>
       <c r="E315" s="11" t="n"/>
       <c r="F315" s="11" t="n"/>
-      <c r="G315" s="14" t="n"/>
+      <c r="G315" s="11" t="n"/>
+      <c r="H315" s="14" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="11" t="n"/>
@@ -58219,7 +58548,8 @@
       <c r="D316" s="11" t="n"/>
       <c r="E316" s="11" t="n"/>
       <c r="F316" s="11" t="n"/>
-      <c r="G316" s="14" t="n"/>
+      <c r="G316" s="11" t="n"/>
+      <c r="H316" s="14" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="11" t="n"/>
@@ -58228,7 +58558,8 @@
       <c r="D317" s="11" t="n"/>
       <c r="E317" s="11" t="n"/>
       <c r="F317" s="11" t="n"/>
-      <c r="G317" s="14" t="n"/>
+      <c r="G317" s="11" t="n"/>
+      <c r="H317" s="14" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="11" t="n"/>
@@ -58237,7 +58568,8 @@
       <c r="D318" s="11" t="n"/>
       <c r="E318" s="11" t="n"/>
       <c r="F318" s="11" t="n"/>
-      <c r="G318" s="14" t="n"/>
+      <c r="G318" s="11" t="n"/>
+      <c r="H318" s="14" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="11" t="n"/>
@@ -58246,7 +58578,8 @@
       <c r="D319" s="11" t="n"/>
       <c r="E319" s="11" t="n"/>
       <c r="F319" s="11" t="n"/>
-      <c r="G319" s="14" t="n"/>
+      <c r="G319" s="11" t="n"/>
+      <c r="H319" s="14" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="11" t="n"/>
@@ -58255,7 +58588,8 @@
       <c r="D320" s="11" t="n"/>
       <c r="E320" s="11" t="n"/>
       <c r="F320" s="11" t="n"/>
-      <c r="G320" s="14" t="n"/>
+      <c r="G320" s="11" t="n"/>
+      <c r="H320" s="14" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="11" t="n"/>
@@ -58264,7 +58598,8 @@
       <c r="D321" s="11" t="n"/>
       <c r="E321" s="11" t="n"/>
       <c r="F321" s="11" t="n"/>
-      <c r="G321" s="14" t="n"/>
+      <c r="G321" s="11" t="n"/>
+      <c r="H321" s="14" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="11" t="n"/>
@@ -58273,7 +58608,8 @@
       <c r="D322" s="11" t="n"/>
       <c r="E322" s="11" t="n"/>
       <c r="F322" s="11" t="n"/>
-      <c r="G322" s="14" t="n"/>
+      <c r="G322" s="11" t="n"/>
+      <c r="H322" s="14" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="11" t="n"/>
@@ -58282,7 +58618,8 @@
       <c r="D323" s="11" t="n"/>
       <c r="E323" s="11" t="n"/>
       <c r="F323" s="11" t="n"/>
-      <c r="G323" s="14" t="n"/>
+      <c r="G323" s="11" t="n"/>
+      <c r="H323" s="14" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="11" t="n"/>
@@ -58291,7 +58628,8 @@
       <c r="D324" s="11" t="n"/>
       <c r="E324" s="11" t="n"/>
       <c r="F324" s="11" t="n"/>
-      <c r="G324" s="14" t="n"/>
+      <c r="G324" s="11" t="n"/>
+      <c r="H324" s="14" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="11" t="n"/>
@@ -58300,7 +58638,8 @@
       <c r="D325" s="11" t="n"/>
       <c r="E325" s="11" t="n"/>
       <c r="F325" s="11" t="n"/>
-      <c r="G325" s="14" t="n"/>
+      <c r="G325" s="11" t="n"/>
+      <c r="H325" s="14" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="11" t="n"/>
@@ -58309,7 +58648,8 @@
       <c r="D326" s="11" t="n"/>
       <c r="E326" s="11" t="n"/>
       <c r="F326" s="11" t="n"/>
-      <c r="G326" s="14" t="n"/>
+      <c r="G326" s="11" t="n"/>
+      <c r="H326" s="14" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="11" t="n"/>
@@ -58318,7 +58658,8 @@
       <c r="D327" s="11" t="n"/>
       <c r="E327" s="11" t="n"/>
       <c r="F327" s="11" t="n"/>
-      <c r="G327" s="14" t="n"/>
+      <c r="G327" s="11" t="n"/>
+      <c r="H327" s="14" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="11" t="n"/>
@@ -58327,7 +58668,8 @@
       <c r="D328" s="11" t="n"/>
       <c r="E328" s="11" t="n"/>
       <c r="F328" s="11" t="n"/>
-      <c r="G328" s="14" t="n"/>
+      <c r="G328" s="11" t="n"/>
+      <c r="H328" s="14" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="11" t="n"/>
@@ -58336,7 +58678,8 @@
       <c r="D329" s="11" t="n"/>
       <c r="E329" s="11" t="n"/>
       <c r="F329" s="11" t="n"/>
-      <c r="G329" s="14" t="n"/>
+      <c r="G329" s="11" t="n"/>
+      <c r="H329" s="14" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="11" t="n"/>
@@ -58345,7 +58688,8 @@
       <c r="D330" s="11" t="n"/>
       <c r="E330" s="11" t="n"/>
       <c r="F330" s="11" t="n"/>
-      <c r="G330" s="14" t="n"/>
+      <c r="G330" s="11" t="n"/>
+      <c r="H330" s="14" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="11" t="n"/>
@@ -58354,7 +58698,8 @@
       <c r="D331" s="11" t="n"/>
       <c r="E331" s="11" t="n"/>
       <c r="F331" s="11" t="n"/>
-      <c r="G331" s="14" t="n"/>
+      <c r="G331" s="11" t="n"/>
+      <c r="H331" s="14" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="11" t="n"/>
@@ -58363,7 +58708,8 @@
       <c r="D332" s="11" t="n"/>
       <c r="E332" s="11" t="n"/>
       <c r="F332" s="11" t="n"/>
-      <c r="G332" s="14" t="n"/>
+      <c r="G332" s="11" t="n"/>
+      <c r="H332" s="14" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="11" t="n"/>
@@ -58372,7 +58718,8 @@
       <c r="D333" s="11" t="n"/>
       <c r="E333" s="11" t="n"/>
       <c r="F333" s="11" t="n"/>
-      <c r="G333" s="14" t="n"/>
+      <c r="G333" s="11" t="n"/>
+      <c r="H333" s="14" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="11" t="n"/>
@@ -58381,7 +58728,8 @@
       <c r="D334" s="11" t="n"/>
       <c r="E334" s="11" t="n"/>
       <c r="F334" s="11" t="n"/>
-      <c r="G334" s="14" t="n"/>
+      <c r="G334" s="11" t="n"/>
+      <c r="H334" s="14" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="11" t="n"/>
@@ -58390,7 +58738,8 @@
       <c r="D335" s="11" t="n"/>
       <c r="E335" s="11" t="n"/>
       <c r="F335" s="11" t="n"/>
-      <c r="G335" s="14" t="n"/>
+      <c r="G335" s="11" t="n"/>
+      <c r="H335" s="14" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="11" t="n"/>
@@ -58399,7 +58748,8 @@
       <c r="D336" s="11" t="n"/>
       <c r="E336" s="11" t="n"/>
       <c r="F336" s="11" t="n"/>
-      <c r="G336" s="14" t="n"/>
+      <c r="G336" s="11" t="n"/>
+      <c r="H336" s="14" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="11" t="n"/>
@@ -58408,7 +58758,8 @@
       <c r="D337" s="11" t="n"/>
       <c r="E337" s="11" t="n"/>
       <c r="F337" s="11" t="n"/>
-      <c r="G337" s="14" t="n"/>
+      <c r="G337" s="11" t="n"/>
+      <c r="H337" s="14" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="11" t="n"/>
@@ -58417,7 +58768,8 @@
       <c r="D338" s="11" t="n"/>
       <c r="E338" s="11" t="n"/>
       <c r="F338" s="11" t="n"/>
-      <c r="G338" s="14" t="n"/>
+      <c r="G338" s="11" t="n"/>
+      <c r="H338" s="14" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="11" t="n"/>
@@ -58426,7 +58778,8 @@
       <c r="D339" s="11" t="n"/>
       <c r="E339" s="11" t="n"/>
       <c r="F339" s="11" t="n"/>
-      <c r="G339" s="14" t="n"/>
+      <c r="G339" s="11" t="n"/>
+      <c r="H339" s="14" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="11" t="n"/>
@@ -58435,7 +58788,8 @@
       <c r="D340" s="11" t="n"/>
       <c r="E340" s="11" t="n"/>
       <c r="F340" s="11" t="n"/>
-      <c r="G340" s="14" t="n"/>
+      <c r="G340" s="11" t="n"/>
+      <c r="H340" s="14" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="11" t="n"/>
@@ -58444,7 +58798,8 @@
       <c r="D341" s="11" t="n"/>
       <c r="E341" s="11" t="n"/>
       <c r="F341" s="11" t="n"/>
-      <c r="G341" s="14" t="n"/>
+      <c r="G341" s="11" t="n"/>
+      <c r="H341" s="14" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="11" t="n"/>
@@ -58453,7 +58808,8 @@
       <c r="D342" s="11" t="n"/>
       <c r="E342" s="11" t="n"/>
       <c r="F342" s="11" t="n"/>
-      <c r="G342" s="14" t="n"/>
+      <c r="G342" s="11" t="n"/>
+      <c r="H342" s="14" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="11" t="n"/>
@@ -58462,7 +58818,8 @@
       <c r="D343" s="11" t="n"/>
       <c r="E343" s="11" t="n"/>
       <c r="F343" s="11" t="n"/>
-      <c r="G343" s="14" t="n"/>
+      <c r="G343" s="11" t="n"/>
+      <c r="H343" s="14" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="11" t="n"/>
@@ -58471,7 +58828,8 @@
       <c r="D344" s="11" t="n"/>
       <c r="E344" s="11" t="n"/>
       <c r="F344" s="11" t="n"/>
-      <c r="G344" s="14" t="n"/>
+      <c r="G344" s="11" t="n"/>
+      <c r="H344" s="14" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="11" t="n"/>
@@ -58480,7 +58838,8 @@
       <c r="D345" s="11" t="n"/>
       <c r="E345" s="11" t="n"/>
       <c r="F345" s="11" t="n"/>
-      <c r="G345" s="14" t="n"/>
+      <c r="G345" s="11" t="n"/>
+      <c r="H345" s="14" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="11" t="n"/>
@@ -58489,7 +58848,8 @@
       <c r="D346" s="11" t="n"/>
       <c r="E346" s="11" t="n"/>
       <c r="F346" s="11" t="n"/>
-      <c r="G346" s="14" t="n"/>
+      <c r="G346" s="11" t="n"/>
+      <c r="H346" s="14" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="11" t="n"/>
@@ -58498,7 +58858,8 @@
       <c r="D347" s="11" t="n"/>
       <c r="E347" s="11" t="n"/>
       <c r="F347" s="11" t="n"/>
-      <c r="G347" s="14" t="n"/>
+      <c r="G347" s="11" t="n"/>
+      <c r="H347" s="14" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="11" t="n"/>
@@ -58507,7 +58868,8 @@
       <c r="D348" s="11" t="n"/>
       <c r="E348" s="11" t="n"/>
       <c r="F348" s="11" t="n"/>
-      <c r="G348" s="14" t="n"/>
+      <c r="G348" s="11" t="n"/>
+      <c r="H348" s="14" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="11" t="n"/>
@@ -58516,7 +58878,8 @@
       <c r="D349" s="11" t="n"/>
       <c r="E349" s="11" t="n"/>
       <c r="F349" s="11" t="n"/>
-      <c r="G349" s="14" t="n"/>
+      <c r="G349" s="11" t="n"/>
+      <c r="H349" s="14" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="11" t="n"/>
@@ -58525,7 +58888,8 @@
       <c r="D350" s="11" t="n"/>
       <c r="E350" s="11" t="n"/>
       <c r="F350" s="11" t="n"/>
-      <c r="G350" s="14" t="n"/>
+      <c r="G350" s="11" t="n"/>
+      <c r="H350" s="14" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="11" t="n"/>
@@ -58534,7 +58898,8 @@
       <c r="D351" s="11" t="n"/>
       <c r="E351" s="11" t="n"/>
       <c r="F351" s="11" t="n"/>
-      <c r="G351" s="14" t="n"/>
+      <c r="G351" s="11" t="n"/>
+      <c r="H351" s="14" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="11" t="n"/>
@@ -58543,7 +58908,8 @@
       <c r="D352" s="11" t="n"/>
       <c r="E352" s="11" t="n"/>
       <c r="F352" s="11" t="n"/>
-      <c r="G352" s="14" t="n"/>
+      <c r="G352" s="11" t="n"/>
+      <c r="H352" s="14" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="11" t="n"/>
@@ -58552,7 +58918,8 @@
       <c r="D353" s="11" t="n"/>
       <c r="E353" s="11" t="n"/>
       <c r="F353" s="11" t="n"/>
-      <c r="G353" s="14" t="n"/>
+      <c r="G353" s="11" t="n"/>
+      <c r="H353" s="14" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="11" t="n"/>
@@ -58561,7 +58928,8 @@
       <c r="D354" s="11" t="n"/>
       <c r="E354" s="11" t="n"/>
       <c r="F354" s="11" t="n"/>
-      <c r="G354" s="14" t="n"/>
+      <c r="G354" s="11" t="n"/>
+      <c r="H354" s="14" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="11" t="n"/>
@@ -58570,7 +58938,8 @@
       <c r="D355" s="11" t="n"/>
       <c r="E355" s="11" t="n"/>
       <c r="F355" s="11" t="n"/>
-      <c r="G355" s="14" t="n"/>
+      <c r="G355" s="11" t="n"/>
+      <c r="H355" s="14" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="11" t="n"/>
@@ -58579,7 +58948,8 @@
       <c r="D356" s="11" t="n"/>
       <c r="E356" s="11" t="n"/>
       <c r="F356" s="11" t="n"/>
-      <c r="G356" s="14" t="n"/>
+      <c r="G356" s="11" t="n"/>
+      <c r="H356" s="14" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="11" t="n"/>
@@ -58588,7 +58958,8 @@
       <c r="D357" s="11" t="n"/>
       <c r="E357" s="11" t="n"/>
       <c r="F357" s="11" t="n"/>
-      <c r="G357" s="14" t="n"/>
+      <c r="G357" s="11" t="n"/>
+      <c r="H357" s="14" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="11" t="n"/>
@@ -58597,7 +58968,8 @@
       <c r="D358" s="11" t="n"/>
       <c r="E358" s="11" t="n"/>
       <c r="F358" s="11" t="n"/>
-      <c r="G358" s="14" t="n"/>
+      <c r="G358" s="11" t="n"/>
+      <c r="H358" s="14" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="11" t="n"/>
@@ -58606,7 +58978,8 @@
       <c r="D359" s="11" t="n"/>
       <c r="E359" s="11" t="n"/>
       <c r="F359" s="11" t="n"/>
-      <c r="G359" s="14" t="n"/>
+      <c r="G359" s="11" t="n"/>
+      <c r="H359" s="14" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="11" t="n"/>
@@ -58615,7 +58988,8 @@
       <c r="D360" s="11" t="n"/>
       <c r="E360" s="11" t="n"/>
       <c r="F360" s="11" t="n"/>
-      <c r="G360" s="14" t="n"/>
+      <c r="G360" s="11" t="n"/>
+      <c r="H360" s="14" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="11" t="n"/>
@@ -58624,7 +58998,8 @@
       <c r="D361" s="11" t="n"/>
       <c r="E361" s="11" t="n"/>
       <c r="F361" s="11" t="n"/>
-      <c r="G361" s="14" t="n"/>
+      <c r="G361" s="11" t="n"/>
+      <c r="H361" s="14" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="11" t="n"/>
@@ -58633,7 +59008,8 @@
       <c r="D362" s="11" t="n"/>
       <c r="E362" s="11" t="n"/>
       <c r="F362" s="11" t="n"/>
-      <c r="G362" s="14" t="n"/>
+      <c r="G362" s="11" t="n"/>
+      <c r="H362" s="14" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="11" t="n"/>
@@ -58642,7 +59018,8 @@
       <c r="D363" s="11" t="n"/>
       <c r="E363" s="11" t="n"/>
       <c r="F363" s="11" t="n"/>
-      <c r="G363" s="14" t="n"/>
+      <c r="G363" s="11" t="n"/>
+      <c r="H363" s="14" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="11" t="n"/>
@@ -58651,7 +59028,8 @@
       <c r="D364" s="11" t="n"/>
       <c r="E364" s="11" t="n"/>
       <c r="F364" s="11" t="n"/>
-      <c r="G364" s="14" t="n"/>
+      <c r="G364" s="11" t="n"/>
+      <c r="H364" s="14" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="11" t="n"/>
@@ -58660,7 +59038,8 @@
       <c r="D365" s="11" t="n"/>
       <c r="E365" s="11" t="n"/>
       <c r="F365" s="11" t="n"/>
-      <c r="G365" s="14" t="n"/>
+      <c r="G365" s="11" t="n"/>
+      <c r="H365" s="14" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="11" t="n"/>
@@ -58669,7 +59048,8 @@
       <c r="D366" s="11" t="n"/>
       <c r="E366" s="11" t="n"/>
       <c r="F366" s="11" t="n"/>
-      <c r="G366" s="14" t="n"/>
+      <c r="G366" s="11" t="n"/>
+      <c r="H366" s="14" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="11" t="n"/>
@@ -58678,7 +59058,8 @@
       <c r="D367" s="11" t="n"/>
       <c r="E367" s="11" t="n"/>
       <c r="F367" s="11" t="n"/>
-      <c r="G367" s="14" t="n"/>
+      <c r="G367" s="11" t="n"/>
+      <c r="H367" s="14" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="11" t="n"/>
@@ -58687,7 +59068,8 @@
       <c r="D368" s="11" t="n"/>
       <c r="E368" s="11" t="n"/>
       <c r="F368" s="11" t="n"/>
-      <c r="G368" s="14" t="n"/>
+      <c r="G368" s="11" t="n"/>
+      <c r="H368" s="14" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="11" t="n"/>
@@ -58696,7 +59078,8 @@
       <c r="D369" s="11" t="n"/>
       <c r="E369" s="11" t="n"/>
       <c r="F369" s="11" t="n"/>
-      <c r="G369" s="14" t="n"/>
+      <c r="G369" s="11" t="n"/>
+      <c r="H369" s="14" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="11" t="n"/>
@@ -58705,7 +59088,8 @@
       <c r="D370" s="11" t="n"/>
       <c r="E370" s="11" t="n"/>
       <c r="F370" s="11" t="n"/>
-      <c r="G370" s="14" t="n"/>
+      <c r="G370" s="11" t="n"/>
+      <c r="H370" s="14" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="11" t="n"/>
@@ -58714,7 +59098,8 @@
       <c r="D371" s="11" t="n"/>
       <c r="E371" s="11" t="n"/>
       <c r="F371" s="11" t="n"/>
-      <c r="G371" s="14" t="n"/>
+      <c r="G371" s="11" t="n"/>
+      <c r="H371" s="14" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="11" t="n"/>
@@ -58723,7 +59108,8 @@
       <c r="D372" s="11" t="n"/>
       <c r="E372" s="11" t="n"/>
       <c r="F372" s="11" t="n"/>
-      <c r="G372" s="14" t="n"/>
+      <c r="G372" s="11" t="n"/>
+      <c r="H372" s="14" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="11" t="n"/>
@@ -58732,7 +59118,8 @@
       <c r="D373" s="11" t="n"/>
       <c r="E373" s="11" t="n"/>
       <c r="F373" s="11" t="n"/>
-      <c r="G373" s="14" t="n"/>
+      <c r="G373" s="11" t="n"/>
+      <c r="H373" s="14" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="11" t="n"/>
@@ -58741,7 +59128,8 @@
       <c r="D374" s="11" t="n"/>
       <c r="E374" s="11" t="n"/>
       <c r="F374" s="11" t="n"/>
-      <c r="G374" s="14" t="n"/>
+      <c r="G374" s="11" t="n"/>
+      <c r="H374" s="14" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="11" t="n"/>
@@ -58750,7 +59138,8 @@
       <c r="D375" s="11" t="n"/>
       <c r="E375" s="11" t="n"/>
       <c r="F375" s="11" t="n"/>
-      <c r="G375" s="14" t="n"/>
+      <c r="G375" s="11" t="n"/>
+      <c r="H375" s="14" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="11" t="n"/>
@@ -58759,7 +59148,8 @@
       <c r="D376" s="11" t="n"/>
       <c r="E376" s="11" t="n"/>
       <c r="F376" s="11" t="n"/>
-      <c r="G376" s="14" t="n"/>
+      <c r="G376" s="11" t="n"/>
+      <c r="H376" s="14" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="11" t="n"/>
@@ -58768,7 +59158,8 @@
       <c r="D377" s="11" t="n"/>
       <c r="E377" s="11" t="n"/>
       <c r="F377" s="11" t="n"/>
-      <c r="G377" s="14" t="n"/>
+      <c r="G377" s="11" t="n"/>
+      <c r="H377" s="14" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="11" t="n"/>
@@ -58777,7 +59168,8 @@
       <c r="D378" s="11" t="n"/>
       <c r="E378" s="11" t="n"/>
       <c r="F378" s="11" t="n"/>
-      <c r="G378" s="14" t="n"/>
+      <c r="G378" s="11" t="n"/>
+      <c r="H378" s="14" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="11" t="n"/>
@@ -58786,7 +59178,8 @@
       <c r="D379" s="11" t="n"/>
       <c r="E379" s="11" t="n"/>
       <c r="F379" s="11" t="n"/>
-      <c r="G379" s="14" t="n"/>
+      <c r="G379" s="11" t="n"/>
+      <c r="H379" s="14" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="11" t="n"/>
@@ -58795,7 +59188,8 @@
       <c r="D380" s="11" t="n"/>
       <c r="E380" s="11" t="n"/>
       <c r="F380" s="11" t="n"/>
-      <c r="G380" s="14" t="n"/>
+      <c r="G380" s="11" t="n"/>
+      <c r="H380" s="14" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="11" t="n"/>
@@ -58804,7 +59198,8 @@
       <c r="D381" s="11" t="n"/>
       <c r="E381" s="11" t="n"/>
       <c r="F381" s="11" t="n"/>
-      <c r="G381" s="14" t="n"/>
+      <c r="G381" s="11" t="n"/>
+      <c r="H381" s="14" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="11" t="n"/>
@@ -58813,7 +59208,8 @@
       <c r="D382" s="11" t="n"/>
       <c r="E382" s="11" t="n"/>
       <c r="F382" s="11" t="n"/>
-      <c r="G382" s="14" t="n"/>
+      <c r="G382" s="11" t="n"/>
+      <c r="H382" s="14" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="11" t="n"/>
@@ -58822,7 +59218,8 @@
       <c r="D383" s="11" t="n"/>
       <c r="E383" s="11" t="n"/>
       <c r="F383" s="11" t="n"/>
-      <c r="G383" s="14" t="n"/>
+      <c r="G383" s="11" t="n"/>
+      <c r="H383" s="14" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="11" t="n"/>
@@ -58831,7 +59228,8 @@
       <c r="D384" s="11" t="n"/>
       <c r="E384" s="11" t="n"/>
       <c r="F384" s="11" t="n"/>
-      <c r="G384" s="14" t="n"/>
+      <c r="G384" s="11" t="n"/>
+      <c r="H384" s="14" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="11" t="n"/>
@@ -58840,7 +59238,8 @@
       <c r="D385" s="11" t="n"/>
       <c r="E385" s="11" t="n"/>
       <c r="F385" s="11" t="n"/>
-      <c r="G385" s="14" t="n"/>
+      <c r="G385" s="11" t="n"/>
+      <c r="H385" s="14" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="11" t="n"/>
@@ -58849,7 +59248,8 @@
       <c r="D386" s="11" t="n"/>
       <c r="E386" s="11" t="n"/>
       <c r="F386" s="11" t="n"/>
-      <c r="G386" s="14" t="n"/>
+      <c r="G386" s="11" t="n"/>
+      <c r="H386" s="14" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="11" t="n"/>
@@ -58858,7 +59258,8 @@
       <c r="D387" s="11" t="n"/>
       <c r="E387" s="11" t="n"/>
       <c r="F387" s="11" t="n"/>
-      <c r="G387" s="14" t="n"/>
+      <c r="G387" s="11" t="n"/>
+      <c r="H387" s="14" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="11" t="n"/>
@@ -58867,7 +59268,8 @@
       <c r="D388" s="11" t="n"/>
       <c r="E388" s="11" t="n"/>
       <c r="F388" s="11" t="n"/>
-      <c r="G388" s="14" t="n"/>
+      <c r="G388" s="11" t="n"/>
+      <c r="H388" s="14" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="11" t="n"/>
@@ -58876,7 +59278,8 @@
       <c r="D389" s="11" t="n"/>
       <c r="E389" s="11" t="n"/>
       <c r="F389" s="11" t="n"/>
-      <c r="G389" s="14" t="n"/>
+      <c r="G389" s="11" t="n"/>
+      <c r="H389" s="14" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="11" t="n"/>
@@ -58885,7 +59288,8 @@
       <c r="D390" s="11" t="n"/>
       <c r="E390" s="11" t="n"/>
       <c r="F390" s="11" t="n"/>
-      <c r="G390" s="14" t="n"/>
+      <c r="G390" s="11" t="n"/>
+      <c r="H390" s="14" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="11" t="n"/>
@@ -58894,7 +59298,8 @@
       <c r="D391" s="11" t="n"/>
       <c r="E391" s="11" t="n"/>
       <c r="F391" s="11" t="n"/>
-      <c r="G391" s="14" t="n"/>
+      <c r="G391" s="11" t="n"/>
+      <c r="H391" s="14" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="11" t="n"/>
@@ -58903,7 +59308,8 @@
       <c r="D392" s="11" t="n"/>
       <c r="E392" s="11" t="n"/>
       <c r="F392" s="11" t="n"/>
-      <c r="G392" s="14" t="n"/>
+      <c r="G392" s="11" t="n"/>
+      <c r="H392" s="14" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="11" t="n"/>
@@ -58912,7 +59318,8 @@
       <c r="D393" s="11" t="n"/>
       <c r="E393" s="11" t="n"/>
       <c r="F393" s="11" t="n"/>
-      <c r="G393" s="14" t="n"/>
+      <c r="G393" s="11" t="n"/>
+      <c r="H393" s="14" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="11" t="n"/>
@@ -58921,7 +59328,8 @@
       <c r="D394" s="11" t="n"/>
       <c r="E394" s="11" t="n"/>
       <c r="F394" s="11" t="n"/>
-      <c r="G394" s="14" t="n"/>
+      <c r="G394" s="11" t="n"/>
+      <c r="H394" s="14" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="11" t="n"/>
@@ -58930,7 +59338,8 @@
       <c r="D395" s="11" t="n"/>
       <c r="E395" s="11" t="n"/>
       <c r="F395" s="11" t="n"/>
-      <c r="G395" s="14" t="n"/>
+      <c r="G395" s="11" t="n"/>
+      <c r="H395" s="14" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="11" t="n"/>
@@ -58939,7 +59348,8 @@
       <c r="D396" s="11" t="n"/>
       <c r="E396" s="11" t="n"/>
       <c r="F396" s="11" t="n"/>
-      <c r="G396" s="14" t="n"/>
+      <c r="G396" s="11" t="n"/>
+      <c r="H396" s="14" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="11" t="n"/>
@@ -58948,7 +59358,8 @@
       <c r="D397" s="11" t="n"/>
       <c r="E397" s="11" t="n"/>
       <c r="F397" s="11" t="n"/>
-      <c r="G397" s="14" t="n"/>
+      <c r="G397" s="11" t="n"/>
+      <c r="H397" s="14" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="11" t="n"/>
@@ -58957,7 +59368,8 @@
       <c r="D398" s="11" t="n"/>
       <c r="E398" s="11" t="n"/>
       <c r="F398" s="11" t="n"/>
-      <c r="G398" s="14" t="n"/>
+      <c r="G398" s="11" t="n"/>
+      <c r="H398" s="14" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="11" t="n"/>
@@ -58966,7 +59378,8 @@
       <c r="D399" s="11" t="n"/>
       <c r="E399" s="11" t="n"/>
       <c r="F399" s="11" t="n"/>
-      <c r="G399" s="14" t="n"/>
+      <c r="G399" s="11" t="n"/>
+      <c r="H399" s="14" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="11" t="n"/>
@@ -58975,7 +59388,8 @@
       <c r="D400" s="11" t="n"/>
       <c r="E400" s="11" t="n"/>
       <c r="F400" s="11" t="n"/>
-      <c r="G400" s="14" t="n"/>
+      <c r="G400" s="11" t="n"/>
+      <c r="H400" s="14" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="11" t="n"/>
@@ -58984,7 +59398,8 @@
       <c r="D401" s="11" t="n"/>
       <c r="E401" s="11" t="n"/>
       <c r="F401" s="11" t="n"/>
-      <c r="G401" s="14" t="n"/>
+      <c r="G401" s="11" t="n"/>
+      <c r="H401" s="14" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="11" t="n"/>
@@ -58993,7 +59408,8 @@
       <c r="D402" s="11" t="n"/>
       <c r="E402" s="11" t="n"/>
       <c r="F402" s="11" t="n"/>
-      <c r="G402" s="14" t="n"/>
+      <c r="G402" s="11" t="n"/>
+      <c r="H402" s="14" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="11" t="n"/>
@@ -59002,7 +59418,8 @@
       <c r="D403" s="11" t="n"/>
       <c r="E403" s="11" t="n"/>
       <c r="F403" s="11" t="n"/>
-      <c r="G403" s="14" t="n"/>
+      <c r="G403" s="11" t="n"/>
+      <c r="H403" s="14" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="11" t="n"/>
@@ -59011,7 +59428,8 @@
       <c r="D404" s="11" t="n"/>
       <c r="E404" s="11" t="n"/>
       <c r="F404" s="11" t="n"/>
-      <c r="G404" s="14" t="n"/>
+      <c r="G404" s="11" t="n"/>
+      <c r="H404" s="14" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="11" t="n"/>
@@ -59020,7 +59438,8 @@
       <c r="D405" s="11" t="n"/>
       <c r="E405" s="11" t="n"/>
       <c r="F405" s="11" t="n"/>
-      <c r="G405" s="14" t="n"/>
+      <c r="G405" s="11" t="n"/>
+      <c r="H405" s="14" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="11" t="n"/>
@@ -59029,7 +59448,8 @@
       <c r="D406" s="11" t="n"/>
       <c r="E406" s="11" t="n"/>
       <c r="F406" s="11" t="n"/>
-      <c r="G406" s="14" t="n"/>
+      <c r="G406" s="11" t="n"/>
+      <c r="H406" s="14" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="11" t="n"/>
@@ -59038,7 +59458,8 @@
       <c r="D407" s="11" t="n"/>
       <c r="E407" s="11" t="n"/>
       <c r="F407" s="11" t="n"/>
-      <c r="G407" s="14" t="n"/>
+      <c r="G407" s="11" t="n"/>
+      <c r="H407" s="14" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="11" t="n"/>
@@ -59047,7 +59468,8 @@
       <c r="D408" s="11" t="n"/>
       <c r="E408" s="11" t="n"/>
       <c r="F408" s="11" t="n"/>
-      <c r="G408" s="14" t="n"/>
+      <c r="G408" s="11" t="n"/>
+      <c r="H408" s="14" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="11" t="n"/>
@@ -59056,7 +59478,8 @@
       <c r="D409" s="11" t="n"/>
       <c r="E409" s="11" t="n"/>
       <c r="F409" s="11" t="n"/>
-      <c r="G409" s="14" t="n"/>
+      <c r="G409" s="11" t="n"/>
+      <c r="H409" s="14" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="11" t="n"/>
@@ -59065,7 +59488,8 @@
       <c r="D410" s="11" t="n"/>
       <c r="E410" s="11" t="n"/>
       <c r="F410" s="11" t="n"/>
-      <c r="G410" s="14" t="n"/>
+      <c r="G410" s="11" t="n"/>
+      <c r="H410" s="14" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="11" t="n"/>
@@ -59074,7 +59498,8 @@
       <c r="D411" s="11" t="n"/>
       <c r="E411" s="11" t="n"/>
       <c r="F411" s="11" t="n"/>
-      <c r="G411" s="14" t="n"/>
+      <c r="G411" s="11" t="n"/>
+      <c r="H411" s="14" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="11" t="n"/>
@@ -59083,7 +59508,8 @@
       <c r="D412" s="11" t="n"/>
       <c r="E412" s="11" t="n"/>
       <c r="F412" s="11" t="n"/>
-      <c r="G412" s="14" t="n"/>
+      <c r="G412" s="11" t="n"/>
+      <c r="H412" s="14" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="11" t="n"/>
@@ -59092,7 +59518,8 @@
       <c r="D413" s="11" t="n"/>
       <c r="E413" s="11" t="n"/>
       <c r="F413" s="11" t="n"/>
-      <c r="G413" s="14" t="n"/>
+      <c r="G413" s="11" t="n"/>
+      <c r="H413" s="14" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="11" t="n"/>
@@ -59101,7 +59528,8 @@
       <c r="D414" s="11" t="n"/>
       <c r="E414" s="11" t="n"/>
       <c r="F414" s="11" t="n"/>
-      <c r="G414" s="14" t="n"/>
+      <c r="G414" s="11" t="n"/>
+      <c r="H414" s="14" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="11" t="n"/>
@@ -59110,7 +59538,8 @@
       <c r="D415" s="11" t="n"/>
       <c r="E415" s="11" t="n"/>
       <c r="F415" s="11" t="n"/>
-      <c r="G415" s="14" t="n"/>
+      <c r="G415" s="11" t="n"/>
+      <c r="H415" s="14" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="11" t="n"/>
@@ -59119,7 +59548,8 @@
       <c r="D416" s="11" t="n"/>
       <c r="E416" s="11" t="n"/>
       <c r="F416" s="11" t="n"/>
-      <c r="G416" s="14" t="n"/>
+      <c r="G416" s="11" t="n"/>
+      <c r="H416" s="14" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="11" t="n"/>
@@ -59128,7 +59558,8 @@
       <c r="D417" s="11" t="n"/>
       <c r="E417" s="11" t="n"/>
       <c r="F417" s="11" t="n"/>
-      <c r="G417" s="14" t="n"/>
+      <c r="G417" s="11" t="n"/>
+      <c r="H417" s="14" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="11" t="n"/>
@@ -59137,7 +59568,8 @@
       <c r="D418" s="11" t="n"/>
       <c r="E418" s="11" t="n"/>
       <c r="F418" s="11" t="n"/>
-      <c r="G418" s="14" t="n"/>
+      <c r="G418" s="11" t="n"/>
+      <c r="H418" s="14" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="11" t="n"/>
@@ -59146,7 +59578,8 @@
       <c r="D419" s="11" t="n"/>
       <c r="E419" s="11" t="n"/>
       <c r="F419" s="11" t="n"/>
-      <c r="G419" s="14" t="n"/>
+      <c r="G419" s="11" t="n"/>
+      <c r="H419" s="14" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="11" t="n"/>
@@ -59155,7 +59588,8 @@
       <c r="D420" s="11" t="n"/>
       <c r="E420" s="11" t="n"/>
       <c r="F420" s="11" t="n"/>
-      <c r="G420" s="14" t="n"/>
+      <c r="G420" s="11" t="n"/>
+      <c r="H420" s="14" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="11" t="n"/>
@@ -59164,7 +59598,8 @@
       <c r="D421" s="11" t="n"/>
       <c r="E421" s="11" t="n"/>
       <c r="F421" s="11" t="n"/>
-      <c r="G421" s="14" t="n"/>
+      <c r="G421" s="11" t="n"/>
+      <c r="H421" s="14" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="11" t="n"/>
@@ -59173,7 +59608,8 @@
       <c r="D422" s="11" t="n"/>
       <c r="E422" s="11" t="n"/>
       <c r="F422" s="11" t="n"/>
-      <c r="G422" s="14" t="n"/>
+      <c r="G422" s="11" t="n"/>
+      <c r="H422" s="14" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="11" t="n"/>
@@ -59182,7 +59618,8 @@
       <c r="D423" s="11" t="n"/>
       <c r="E423" s="11" t="n"/>
       <c r="F423" s="11" t="n"/>
-      <c r="G423" s="14" t="n"/>
+      <c r="G423" s="11" t="n"/>
+      <c r="H423" s="14" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="11" t="n"/>
@@ -59191,7 +59628,8 @@
       <c r="D424" s="11" t="n"/>
       <c r="E424" s="11" t="n"/>
       <c r="F424" s="11" t="n"/>
-      <c r="G424" s="14" t="n"/>
+      <c r="G424" s="11" t="n"/>
+      <c r="H424" s="14" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="11" t="n"/>
@@ -59200,7 +59638,8 @@
       <c r="D425" s="11" t="n"/>
       <c r="E425" s="11" t="n"/>
       <c r="F425" s="11" t="n"/>
-      <c r="G425" s="14" t="n"/>
+      <c r="G425" s="11" t="n"/>
+      <c r="H425" s="14" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="11" t="n"/>
@@ -59209,7 +59648,8 @@
       <c r="D426" s="11" t="n"/>
       <c r="E426" s="11" t="n"/>
       <c r="F426" s="11" t="n"/>
-      <c r="G426" s="14" t="n"/>
+      <c r="G426" s="11" t="n"/>
+      <c r="H426" s="14" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="11" t="n"/>
@@ -59218,7 +59658,8 @@
       <c r="D427" s="11" t="n"/>
       <c r="E427" s="11" t="n"/>
       <c r="F427" s="11" t="n"/>
-      <c r="G427" s="14" t="n"/>
+      <c r="G427" s="11" t="n"/>
+      <c r="H427" s="14" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="11" t="n"/>
@@ -59227,7 +59668,8 @@
       <c r="D428" s="11" t="n"/>
       <c r="E428" s="11" t="n"/>
       <c r="F428" s="11" t="n"/>
-      <c r="G428" s="14" t="n"/>
+      <c r="G428" s="11" t="n"/>
+      <c r="H428" s="14" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="11" t="n"/>
@@ -59236,7 +59678,8 @@
       <c r="D429" s="11" t="n"/>
       <c r="E429" s="11" t="n"/>
       <c r="F429" s="11" t="n"/>
-      <c r="G429" s="14" t="n"/>
+      <c r="G429" s="11" t="n"/>
+      <c r="H429" s="14" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="11" t="n"/>
@@ -59245,7 +59688,8 @@
       <c r="D430" s="11" t="n"/>
       <c r="E430" s="11" t="n"/>
       <c r="F430" s="11" t="n"/>
-      <c r="G430" s="14" t="n"/>
+      <c r="G430" s="11" t="n"/>
+      <c r="H430" s="14" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="11" t="n"/>
@@ -59254,7 +59698,8 @@
       <c r="D431" s="11" t="n"/>
       <c r="E431" s="11" t="n"/>
       <c r="F431" s="11" t="n"/>
-      <c r="G431" s="14" t="n"/>
+      <c r="G431" s="11" t="n"/>
+      <c r="H431" s="14" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="11" t="n"/>
@@ -59263,7 +59708,8 @@
       <c r="D432" s="11" t="n"/>
       <c r="E432" s="11" t="n"/>
       <c r="F432" s="11" t="n"/>
-      <c r="G432" s="14" t="n"/>
+      <c r="G432" s="11" t="n"/>
+      <c r="H432" s="14" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="11" t="n"/>
@@ -59272,7 +59718,8 @@
       <c r="D433" s="11" t="n"/>
       <c r="E433" s="11" t="n"/>
       <c r="F433" s="11" t="n"/>
-      <c r="G433" s="14" t="n"/>
+      <c r="G433" s="11" t="n"/>
+      <c r="H433" s="14" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="11" t="n"/>
@@ -59281,7 +59728,8 @@
       <c r="D434" s="11" t="n"/>
       <c r="E434" s="11" t="n"/>
       <c r="F434" s="11" t="n"/>
-      <c r="G434" s="14" t="n"/>
+      <c r="G434" s="11" t="n"/>
+      <c r="H434" s="14" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="11" t="n"/>
@@ -59290,7 +59738,8 @@
       <c r="D435" s="11" t="n"/>
       <c r="E435" s="11" t="n"/>
       <c r="F435" s="11" t="n"/>
-      <c r="G435" s="14" t="n"/>
+      <c r="G435" s="11" t="n"/>
+      <c r="H435" s="14" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="11" t="n"/>
@@ -59299,7 +59748,8 @@
       <c r="D436" s="11" t="n"/>
       <c r="E436" s="11" t="n"/>
       <c r="F436" s="11" t="n"/>
-      <c r="G436" s="14" t="n"/>
+      <c r="G436" s="11" t="n"/>
+      <c r="H436" s="14" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="11" t="n"/>
@@ -59308,7 +59758,8 @@
       <c r="D437" s="11" t="n"/>
       <c r="E437" s="11" t="n"/>
       <c r="F437" s="11" t="n"/>
-      <c r="G437" s="14" t="n"/>
+      <c r="G437" s="11" t="n"/>
+      <c r="H437" s="14" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="11" t="n"/>
@@ -59317,7 +59768,8 @@
       <c r="D438" s="11" t="n"/>
       <c r="E438" s="11" t="n"/>
       <c r="F438" s="11" t="n"/>
-      <c r="G438" s="14" t="n"/>
+      <c r="G438" s="11" t="n"/>
+      <c r="H438" s="14" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="11" t="n"/>
@@ -59326,7 +59778,8 @@
       <c r="D439" s="11" t="n"/>
       <c r="E439" s="11" t="n"/>
       <c r="F439" s="11" t="n"/>
-      <c r="G439" s="14" t="n"/>
+      <c r="G439" s="11" t="n"/>
+      <c r="H439" s="14" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="11" t="n"/>
@@ -59335,7 +59788,8 @@
       <c r="D440" s="11" t="n"/>
       <c r="E440" s="11" t="n"/>
       <c r="F440" s="11" t="n"/>
-      <c r="G440" s="14" t="n"/>
+      <c r="G440" s="11" t="n"/>
+      <c r="H440" s="14" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="11" t="n"/>
@@ -59344,7 +59798,8 @@
       <c r="D441" s="11" t="n"/>
       <c r="E441" s="11" t="n"/>
       <c r="F441" s="11" t="n"/>
-      <c r="G441" s="14" t="n"/>
+      <c r="G441" s="11" t="n"/>
+      <c r="H441" s="14" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="11" t="n"/>
@@ -59353,7 +59808,8 @@
       <c r="D442" s="11" t="n"/>
       <c r="E442" s="11" t="n"/>
       <c r="F442" s="11" t="n"/>
-      <c r="G442" s="14" t="n"/>
+      <c r="G442" s="11" t="n"/>
+      <c r="H442" s="14" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="11" t="n"/>
@@ -59362,7 +59818,8 @@
       <c r="D443" s="11" t="n"/>
       <c r="E443" s="11" t="n"/>
       <c r="F443" s="11" t="n"/>
-      <c r="G443" s="14" t="n"/>
+      <c r="G443" s="11" t="n"/>
+      <c r="H443" s="14" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="11" t="n"/>
@@ -59371,7 +59828,8 @@
       <c r="D444" s="11" t="n"/>
       <c r="E444" s="11" t="n"/>
       <c r="F444" s="11" t="n"/>
-      <c r="G444" s="14" t="n"/>
+      <c r="G444" s="11" t="n"/>
+      <c r="H444" s="14" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="11" t="n"/>
@@ -59380,7 +59838,8 @@
       <c r="D445" s="11" t="n"/>
       <c r="E445" s="11" t="n"/>
       <c r="F445" s="11" t="n"/>
-      <c r="G445" s="14" t="n"/>
+      <c r="G445" s="11" t="n"/>
+      <c r="H445" s="14" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="11" t="n"/>
@@ -59389,7 +59848,8 @@
       <c r="D446" s="11" t="n"/>
       <c r="E446" s="11" t="n"/>
       <c r="F446" s="11" t="n"/>
-      <c r="G446" s="14" t="n"/>
+      <c r="G446" s="11" t="n"/>
+      <c r="H446" s="14" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="11" t="n"/>
@@ -59398,7 +59858,8 @@
       <c r="D447" s="11" t="n"/>
       <c r="E447" s="11" t="n"/>
       <c r="F447" s="11" t="n"/>
-      <c r="G447" s="14" t="n"/>
+      <c r="G447" s="11" t="n"/>
+      <c r="H447" s="14" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="11" t="n"/>
@@ -59407,7 +59868,8 @@
       <c r="D448" s="11" t="n"/>
       <c r="E448" s="11" t="n"/>
       <c r="F448" s="11" t="n"/>
-      <c r="G448" s="14" t="n"/>
+      <c r="G448" s="11" t="n"/>
+      <c r="H448" s="14" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="11" t="n"/>
@@ -59416,7 +59878,8 @@
       <c r="D449" s="11" t="n"/>
       <c r="E449" s="11" t="n"/>
       <c r="F449" s="11" t="n"/>
-      <c r="G449" s="14" t="n"/>
+      <c r="G449" s="11" t="n"/>
+      <c r="H449" s="14" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="11" t="n"/>
@@ -59425,7 +59888,8 @@
       <c r="D450" s="11" t="n"/>
       <c r="E450" s="11" t="n"/>
       <c r="F450" s="11" t="n"/>
-      <c r="G450" s="14" t="n"/>
+      <c r="G450" s="11" t="n"/>
+      <c r="H450" s="14" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="11" t="n"/>
@@ -59434,7 +59898,8 @@
       <c r="D451" s="11" t="n"/>
       <c r="E451" s="11" t="n"/>
       <c r="F451" s="11" t="n"/>
-      <c r="G451" s="14" t="n"/>
+      <c r="G451" s="11" t="n"/>
+      <c r="H451" s="14" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="11" t="n"/>
@@ -59443,7 +59908,8 @@
       <c r="D452" s="11" t="n"/>
       <c r="E452" s="11" t="n"/>
       <c r="F452" s="11" t="n"/>
-      <c r="G452" s="14" t="n"/>
+      <c r="G452" s="11" t="n"/>
+      <c r="H452" s="14" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="11" t="n"/>
@@ -59452,7 +59918,8 @@
       <c r="D453" s="11" t="n"/>
       <c r="E453" s="11" t="n"/>
       <c r="F453" s="11" t="n"/>
-      <c r="G453" s="14" t="n"/>
+      <c r="G453" s="11" t="n"/>
+      <c r="H453" s="14" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="11" t="n"/>
@@ -59461,7 +59928,8 @@
       <c r="D454" s="11" t="n"/>
       <c r="E454" s="11" t="n"/>
       <c r="F454" s="11" t="n"/>
-      <c r="G454" s="14" t="n"/>
+      <c r="G454" s="11" t="n"/>
+      <c r="H454" s="14" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="11" t="n"/>
@@ -59470,7 +59938,8 @@
       <c r="D455" s="11" t="n"/>
       <c r="E455" s="11" t="n"/>
       <c r="F455" s="11" t="n"/>
-      <c r="G455" s="14" t="n"/>
+      <c r="G455" s="11" t="n"/>
+      <c r="H455" s="14" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="11" t="n"/>
@@ -59479,7 +59948,8 @@
       <c r="D456" s="11" t="n"/>
       <c r="E456" s="11" t="n"/>
       <c r="F456" s="11" t="n"/>
-      <c r="G456" s="14" t="n"/>
+      <c r="G456" s="11" t="n"/>
+      <c r="H456" s="14" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="11" t="n"/>
@@ -59488,7 +59958,8 @@
       <c r="D457" s="11" t="n"/>
       <c r="E457" s="11" t="n"/>
       <c r="F457" s="11" t="n"/>
-      <c r="G457" s="14" t="n"/>
+      <c r="G457" s="11" t="n"/>
+      <c r="H457" s="14" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="11" t="n"/>
@@ -59497,7 +59968,8 @@
       <c r="D458" s="11" t="n"/>
       <c r="E458" s="11" t="n"/>
       <c r="F458" s="11" t="n"/>
-      <c r="G458" s="14" t="n"/>
+      <c r="G458" s="11" t="n"/>
+      <c r="H458" s="14" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="11" t="n"/>
@@ -59506,7 +59978,8 @@
       <c r="D459" s="11" t="n"/>
       <c r="E459" s="11" t="n"/>
       <c r="F459" s="11" t="n"/>
-      <c r="G459" s="14" t="n"/>
+      <c r="G459" s="11" t="n"/>
+      <c r="H459" s="14" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="11" t="n"/>
@@ -59515,7 +59988,8 @@
       <c r="D460" s="11" t="n"/>
       <c r="E460" s="11" t="n"/>
       <c r="F460" s="11" t="n"/>
-      <c r="G460" s="14" t="n"/>
+      <c r="G460" s="11" t="n"/>
+      <c r="H460" s="14" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="11" t="n"/>
@@ -59524,7 +59998,8 @@
       <c r="D461" s="11" t="n"/>
       <c r="E461" s="11" t="n"/>
       <c r="F461" s="11" t="n"/>
-      <c r="G461" s="14" t="n"/>
+      <c r="G461" s="11" t="n"/>
+      <c r="H461" s="14" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="11" t="n"/>
@@ -59533,7 +60008,8 @@
       <c r="D462" s="11" t="n"/>
       <c r="E462" s="11" t="n"/>
       <c r="F462" s="11" t="n"/>
-      <c r="G462" s="14" t="n"/>
+      <c r="G462" s="11" t="n"/>
+      <c r="H462" s="14" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="11" t="n"/>
@@ -59542,7 +60018,8 @@
       <c r="D463" s="11" t="n"/>
       <c r="E463" s="11" t="n"/>
       <c r="F463" s="11" t="n"/>
-      <c r="G463" s="14" t="n"/>
+      <c r="G463" s="11" t="n"/>
+      <c r="H463" s="14" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="11" t="n"/>
@@ -59551,7 +60028,8 @@
       <c r="D464" s="11" t="n"/>
       <c r="E464" s="11" t="n"/>
       <c r="F464" s="11" t="n"/>
-      <c r="G464" s="14" t="n"/>
+      <c r="G464" s="11" t="n"/>
+      <c r="H464" s="14" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="11" t="n"/>
@@ -59560,7 +60038,8 @@
       <c r="D465" s="11" t="n"/>
       <c r="E465" s="11" t="n"/>
       <c r="F465" s="11" t="n"/>
-      <c r="G465" s="14" t="n"/>
+      <c r="G465" s="11" t="n"/>
+      <c r="H465" s="14" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="11" t="n"/>
@@ -59569,7 +60048,8 @@
       <c r="D466" s="11" t="n"/>
       <c r="E466" s="11" t="n"/>
       <c r="F466" s="11" t="n"/>
-      <c r="G466" s="14" t="n"/>
+      <c r="G466" s="11" t="n"/>
+      <c r="H466" s="14" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="11" t="n"/>
@@ -59578,7 +60058,8 @@
       <c r="D467" s="11" t="n"/>
       <c r="E467" s="11" t="n"/>
       <c r="F467" s="11" t="n"/>
-      <c r="G467" s="14" t="n"/>
+      <c r="G467" s="11" t="n"/>
+      <c r="H467" s="14" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="11" t="n"/>
@@ -59587,7 +60068,8 @@
       <c r="D468" s="11" t="n"/>
       <c r="E468" s="11" t="n"/>
       <c r="F468" s="11" t="n"/>
-      <c r="G468" s="14" t="n"/>
+      <c r="G468" s="11" t="n"/>
+      <c r="H468" s="14" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="11" t="n"/>
@@ -59596,7 +60078,8 @@
       <c r="D469" s="11" t="n"/>
       <c r="E469" s="11" t="n"/>
       <c r="F469" s="11" t="n"/>
-      <c r="G469" s="14" t="n"/>
+      <c r="G469" s="11" t="n"/>
+      <c r="H469" s="14" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="11" t="n"/>
@@ -59605,7 +60088,8 @@
       <c r="D470" s="11" t="n"/>
       <c r="E470" s="11" t="n"/>
       <c r="F470" s="11" t="n"/>
-      <c r="G470" s="14" t="n"/>
+      <c r="G470" s="11" t="n"/>
+      <c r="H470" s="14" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="11" t="n"/>
@@ -59614,7 +60098,8 @@
       <c r="D471" s="11" t="n"/>
       <c r="E471" s="11" t="n"/>
       <c r="F471" s="11" t="n"/>
-      <c r="G471" s="14" t="n"/>
+      <c r="G471" s="11" t="n"/>
+      <c r="H471" s="14" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="11" t="n"/>
@@ -59623,7 +60108,8 @@
       <c r="D472" s="11" t="n"/>
       <c r="E472" s="11" t="n"/>
       <c r="F472" s="11" t="n"/>
-      <c r="G472" s="14" t="n"/>
+      <c r="G472" s="11" t="n"/>
+      <c r="H472" s="14" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="11" t="n"/>
@@ -59632,7 +60118,8 @@
       <c r="D473" s="11" t="n"/>
       <c r="E473" s="11" t="n"/>
       <c r="F473" s="11" t="n"/>
-      <c r="G473" s="14" t="n"/>
+      <c r="G473" s="11" t="n"/>
+      <c r="H473" s="14" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="11" t="n"/>
@@ -59641,7 +60128,8 @@
       <c r="D474" s="11" t="n"/>
       <c r="E474" s="11" t="n"/>
       <c r="F474" s="11" t="n"/>
-      <c r="G474" s="14" t="n"/>
+      <c r="G474" s="11" t="n"/>
+      <c r="H474" s="14" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="11" t="n"/>
@@ -59650,7 +60138,8 @@
       <c r="D475" s="11" t="n"/>
       <c r="E475" s="11" t="n"/>
       <c r="F475" s="11" t="n"/>
-      <c r="G475" s="14" t="n"/>
+      <c r="G475" s="11" t="n"/>
+      <c r="H475" s="14" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="11" t="n"/>
@@ -59659,7 +60148,8 @@
       <c r="D476" s="11" t="n"/>
       <c r="E476" s="11" t="n"/>
       <c r="F476" s="11" t="n"/>
-      <c r="G476" s="14" t="n"/>
+      <c r="G476" s="11" t="n"/>
+      <c r="H476" s="14" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="11" t="n"/>
@@ -59668,7 +60158,8 @@
       <c r="D477" s="11" t="n"/>
       <c r="E477" s="11" t="n"/>
       <c r="F477" s="11" t="n"/>
-      <c r="G477" s="14" t="n"/>
+      <c r="G477" s="11" t="n"/>
+      <c r="H477" s="14" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="11" t="n"/>
@@ -59677,7 +60168,8 @@
       <c r="D478" s="11" t="n"/>
       <c r="E478" s="11" t="n"/>
       <c r="F478" s="11" t="n"/>
-      <c r="G478" s="14" t="n"/>
+      <c r="G478" s="11" t="n"/>
+      <c r="H478" s="14" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="11" t="n"/>
@@ -59686,7 +60178,8 @@
       <c r="D479" s="11" t="n"/>
       <c r="E479" s="11" t="n"/>
       <c r="F479" s="11" t="n"/>
-      <c r="G479" s="14" t="n"/>
+      <c r="G479" s="11" t="n"/>
+      <c r="H479" s="14" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="11" t="n"/>
@@ -59695,7 +60188,8 @@
       <c r="D480" s="11" t="n"/>
       <c r="E480" s="11" t="n"/>
       <c r="F480" s="11" t="n"/>
-      <c r="G480" s="14" t="n"/>
+      <c r="G480" s="11" t="n"/>
+      <c r="H480" s="14" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="11" t="n"/>
@@ -59704,7 +60198,8 @@
       <c r="D481" s="11" t="n"/>
       <c r="E481" s="11" t="n"/>
       <c r="F481" s="11" t="n"/>
-      <c r="G481" s="14" t="n"/>
+      <c r="G481" s="11" t="n"/>
+      <c r="H481" s="14" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="11" t="n"/>
@@ -59713,7 +60208,8 @@
       <c r="D482" s="11" t="n"/>
       <c r="E482" s="11" t="n"/>
       <c r="F482" s="11" t="n"/>
-      <c r="G482" s="14" t="n"/>
+      <c r="G482" s="11" t="n"/>
+      <c r="H482" s="14" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="11" t="n"/>
@@ -59722,7 +60218,8 @@
       <c r="D483" s="11" t="n"/>
       <c r="E483" s="11" t="n"/>
       <c r="F483" s="11" t="n"/>
-      <c r="G483" s="14" t="n"/>
+      <c r="G483" s="11" t="n"/>
+      <c r="H483" s="14" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="11" t="n"/>
@@ -59731,7 +60228,8 @@
       <c r="D484" s="11" t="n"/>
       <c r="E484" s="11" t="n"/>
       <c r="F484" s="11" t="n"/>
-      <c r="G484" s="14" t="n"/>
+      <c r="G484" s="11" t="n"/>
+      <c r="H484" s="14" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="11" t="n"/>
@@ -59740,7 +60238,8 @@
       <c r="D485" s="11" t="n"/>
       <c r="E485" s="11" t="n"/>
       <c r="F485" s="11" t="n"/>
-      <c r="G485" s="14" t="n"/>
+      <c r="G485" s="11" t="n"/>
+      <c r="H485" s="14" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="11" t="n"/>
@@ -59749,7 +60248,8 @@
       <c r="D486" s="11" t="n"/>
       <c r="E486" s="11" t="n"/>
       <c r="F486" s="11" t="n"/>
-      <c r="G486" s="14" t="n"/>
+      <c r="G486" s="11" t="n"/>
+      <c r="H486" s="14" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="11" t="n"/>
@@ -59758,7 +60258,8 @@
       <c r="D487" s="11" t="n"/>
       <c r="E487" s="11" t="n"/>
       <c r="F487" s="11" t="n"/>
-      <c r="G487" s="14" t="n"/>
+      <c r="G487" s="11" t="n"/>
+      <c r="H487" s="14" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="11" t="n"/>
@@ -59767,7 +60268,8 @@
       <c r="D488" s="11" t="n"/>
       <c r="E488" s="11" t="n"/>
       <c r="F488" s="11" t="n"/>
-      <c r="G488" s="14" t="n"/>
+      <c r="G488" s="11" t="n"/>
+      <c r="H488" s="14" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="11" t="n"/>
@@ -59776,7 +60278,8 @@
       <c r="D489" s="11" t="n"/>
       <c r="E489" s="11" t="n"/>
       <c r="F489" s="11" t="n"/>
-      <c r="G489" s="14" t="n"/>
+      <c r="G489" s="11" t="n"/>
+      <c r="H489" s="14" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="11" t="n"/>
@@ -59785,7 +60288,8 @@
       <c r="D490" s="11" t="n"/>
       <c r="E490" s="11" t="n"/>
       <c r="F490" s="11" t="n"/>
-      <c r="G490" s="14" t="n"/>
+      <c r="G490" s="11" t="n"/>
+      <c r="H490" s="14" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="11" t="n"/>
@@ -59794,7 +60298,8 @@
       <c r="D491" s="11" t="n"/>
       <c r="E491" s="11" t="n"/>
       <c r="F491" s="11" t="n"/>
-      <c r="G491" s="14" t="n"/>
+      <c r="G491" s="11" t="n"/>
+      <c r="H491" s="14" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="11" t="n"/>
@@ -59803,7 +60308,8 @@
       <c r="D492" s="11" t="n"/>
       <c r="E492" s="11" t="n"/>
       <c r="F492" s="11" t="n"/>
-      <c r="G492" s="14" t="n"/>
+      <c r="G492" s="11" t="n"/>
+      <c r="H492" s="14" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="11" t="n"/>
@@ -59812,7 +60318,8 @@
       <c r="D493" s="11" t="n"/>
       <c r="E493" s="11" t="n"/>
       <c r="F493" s="11" t="n"/>
-      <c r="G493" s="14" t="n"/>
+      <c r="G493" s="11" t="n"/>
+      <c r="H493" s="14" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="11" t="n"/>
@@ -59821,7 +60328,8 @@
       <c r="D494" s="11" t="n"/>
       <c r="E494" s="11" t="n"/>
       <c r="F494" s="11" t="n"/>
-      <c r="G494" s="14" t="n"/>
+      <c r="G494" s="11" t="n"/>
+      <c r="H494" s="14" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="11" t="n"/>
@@ -59830,7 +60338,8 @@
       <c r="D495" s="11" t="n"/>
       <c r="E495" s="11" t="n"/>
       <c r="F495" s="11" t="n"/>
-      <c r="G495" s="14" t="n"/>
+      <c r="G495" s="11" t="n"/>
+      <c r="H495" s="14" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="11" t="n"/>
@@ -59839,7 +60348,8 @@
       <c r="D496" s="11" t="n"/>
       <c r="E496" s="11" t="n"/>
       <c r="F496" s="11" t="n"/>
-      <c r="G496" s="14" t="n"/>
+      <c r="G496" s="11" t="n"/>
+      <c r="H496" s="14" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="11" t="n"/>
@@ -59848,7 +60358,8 @@
       <c r="D497" s="11" t="n"/>
       <c r="E497" s="11" t="n"/>
       <c r="F497" s="11" t="n"/>
-      <c r="G497" s="14" t="n"/>
+      <c r="G497" s="11" t="n"/>
+      <c r="H497" s="14" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="11" t="n"/>
@@ -59857,7 +60368,8 @@
       <c r="D498" s="11" t="n"/>
       <c r="E498" s="11" t="n"/>
       <c r="F498" s="11" t="n"/>
-      <c r="G498" s="14" t="n"/>
+      <c r="G498" s="11" t="n"/>
+      <c r="H498" s="14" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="11" t="n"/>
@@ -59866,7 +60378,8 @@
       <c r="D499" s="11" t="n"/>
       <c r="E499" s="11" t="n"/>
       <c r="F499" s="11" t="n"/>
-      <c r="G499" s="14" t="n"/>
+      <c r="G499" s="11" t="n"/>
+      <c r="H499" s="14" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="11" t="n"/>
@@ -59875,18 +60388,19 @@
       <c r="D500" s="11" t="n"/>
       <c r="E500" s="11" t="n"/>
       <c r="F500" s="11" t="n"/>
-      <c r="G500" s="14" t="n"/>
+      <c r="G500" s="11" t="n"/>
+      <c r="H500" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G500"/>
+  <autoFilter ref="A1:H500"/>
   <dataValidations count="3">
-    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nepoznata vrednost" error="Izaberi vrednost iz padajućeg menija (vidi list Šifarnici)." type="list">
+    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nepoznata vrednost" error="Izaberi vrednost iz padajućeg menija (vidi list Šifarnici)." type="list">
       <formula1>'Šifarnici'!$L$2:$L$4</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nepoznata vrednost" error="Izaberi vrednost iz padajućeg menija (vidi list Šifarnici)." type="list">
+    <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nepoznata vrednost" error="Izaberi vrednost iz padajućeg menija (vidi list Šifarnici)." type="list">
       <formula1>'Šifarnici'!$M$2:$M$5</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Datum" error="Unesi datum (GGGG-MM-DD)." type="date" operator="between">
+    <dataValidation sqref="H3:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Datum" error="Unesi datum (GGGG-MM-DD)." type="date" operator="between">
       <formula1>DATE(1990,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
